--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>13.55</v>
+        <v>18.69</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>11.66</v>
+        <v>16.8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>16.87</v>
+        <v>20.18</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>16.87</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1076.11</v>
+        <v>15.22</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1076.08</v>
+        <v>12.76</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1076.74</v>
+        <v>15.27</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1076.74</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>175.01</v>
+        <v>1076.35</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>167.54</v>
+        <v>1076.33</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>186.68</v>
+        <v>1076.87</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>187.5</v>
+        <v>1076.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>40.42</v>
+        <v>1079.03</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>36.41</v>
+        <v>1078.77</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46.08</v>
+        <v>1079.56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45.51</v>
+        <v>1079.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>CFEL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>347.99</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>329.02</v>
+        <v>38.58</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>369.05</v>
+        <v>47.41</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>369.05</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>19.97</v>
+        <v>180.66</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19.97</v>
+        <v>171.17</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>21</v>
+        <v>179.89</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.09</v>
+        <v>357.69</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.01</v>
+        <v>340.68</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2.28</v>
+        <v>387.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.29</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1341.88</v>
+        <v>20.45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1340.48</v>
+        <v>20.45</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1405.8</v>
+        <v>21.42</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1405.8</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>670.98</v>
+        <v>2.18</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>625.8200000000001</v>
+        <v>2.13</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>723.15</v>
+        <v>2.38</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>725</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>11.5</v>
+        <v>2.21</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>11.47</v>
+        <v>2.19</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>12.01</v>
+        <v>2.29</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>12.01</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.06</v>
+        <v>11.81</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.06</v>
+        <v>11.69</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.08</v>
+        <v>12.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.08</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>38.57</v>
+        <v>0.06</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>35.9</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>42.4</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>42.6</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1144.02</v>
+        <v>40.54</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1143.92</v>
+        <v>38.04</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1144.6</v>
+        <v>44.4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1144.59</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1098.06</v>
+        <v>1144.24</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1097.94</v>
+        <v>1144.17</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1098.68</v>
+        <v>1144.75</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1098.68</v>
+        <v>1144.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>115.85</v>
+        <v>1098.3</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>115.83</v>
+        <v>1098.15</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>115.91</v>
+        <v>1098.82</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>115.92</v>
+        <v>1098.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1120.71</v>
+        <v>115.88</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1120.69</v>
+        <v>115.86</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1121.3</v>
+        <v>115.92</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1121.3</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>1120.94</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>64.72</v>
+        <v>1120.92</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>70.95</v>
+        <v>1121.45</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>71.7</v>
+        <v>1121.46</v>
       </c>
     </row>
     <row r="19">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>555.86</v>
+        <v>560.79</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>533</v>
+        <v>535.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>560.45</v>
+        <v>568.9</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>300.4</v>
+        <v>315.42</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>300.4</v>
+        <v>315.42</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>330.4</v>
+        <v>346.92</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>330.4</v>
+        <v>346.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2312.84</v>
+        <v>82.77</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2194.38</v>
+        <v>79.05</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2373</v>
+        <v>84.47</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2387.3</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>494.25</v>
+        <v>1.68</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>470.49</v>
+        <v>1.68</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>514.65</v>
+        <v>1.75</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>516.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80.56</v>
+        <v>926</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>76.36</v>
+        <v>825.3200000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>84.23</v>
+        <v>995.95</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>83.98999999999999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.65</v>
+        <v>0.96</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>852.96</v>
+        <v>64.17</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>777.67</v>
+        <v>64.17</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1002.8</v>
+        <v>66.98</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1003</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.92</v>
+        <v>1055.43</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.89</v>
+        <v>1055.41</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.01</v>
+        <v>1055.95</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1.01</v>
+        <v>1055.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,190 +1247,16 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>62.68</v>
+        <v>18.42</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>62.68</v>
+        <v>17.35</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>65.67</v>
+        <v>20.29</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>65.67</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>1055.21</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1055.19</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1055.8</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>1055.8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SHEKHAWATI</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.37</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SYSTMTXC</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>66.34999999999999</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>72.53</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TAMBOLIIN</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>285.43</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>273.73</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>306.85</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TECHNOCRAF</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>426.73</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>397.74</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>442.3</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>437.5</v>
+        <v>20.32</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18.69</v>
+        <v>1076.59</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16.8</v>
+        <v>1076.57</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>20.18</v>
+        <v>1077.02</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>20.3</v>
+        <v>1077.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15.22</v>
+        <v>1079.27</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12.76</v>
+        <v>1079.24</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15.27</v>
+        <v>1079.68</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>15.47</v>
+        <v>1079.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1076.35</v>
+        <v>20.93</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1076.33</v>
+        <v>20.93</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1076.87</v>
+        <v>21.84</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1076.89</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1079.03</v>
+        <v>2.3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1078.77</v>
+        <v>2.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1079.56</v>
+        <v>2.48</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1079.57</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CFEL</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44</v>
+        <v>2.25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>38.58</v>
+        <v>2.25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>47.41</v>
+        <v>2.33</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>47.29</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>180.66</v>
+        <v>1077.64</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>171.17</v>
+        <v>1077.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>179.89</v>
+        <v>1078.05</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>180</v>
+        <v>1078.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>357.69</v>
+        <v>0.06</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>340.68</v>
+        <v>0.06</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>387.5</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>387.5</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20.45</v>
+        <v>42.87</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>20.45</v>
+        <v>40.37</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>21.42</v>
+        <v>46.52</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>21.42</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.18</v>
+        <v>1144.46</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.13</v>
+        <v>1144.42</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.38</v>
+        <v>1144.88</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.39</v>
+        <v>1144.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.21</v>
+        <v>1098.53</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.19</v>
+        <v>1098.38</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.29</v>
+        <v>1098.94</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.29</v>
+        <v>1098.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>11.81</v>
+        <v>115.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>11.69</v>
+        <v>115.88</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>12.6</v>
+        <v>115.93</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>12.61</v>
+        <v>115.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.06</v>
+        <v>1121.17</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.06</v>
+        <v>1121.15</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.08</v>
+        <v>1121.58</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.08</v>
+        <v>1121.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>40.54</v>
+        <v>565.5599999999999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>38.04</v>
+        <v>538.75</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>44.4</v>
+        <v>572.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44.52</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1144.24</v>
+        <v>65.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1144.17</v>
+        <v>65.7</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1144.75</v>
+        <v>68.31</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1144.76</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1098.3</v>
+        <v>1055.66</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1098.15</v>
+        <v>1055.64</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1098.82</v>
+        <v>1056.07</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1098.83</v>
+        <v>1056.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,306 +957,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>115.88</v>
+        <v>19.42</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>115.86</v>
+        <v>18.44</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>115.92</v>
+        <v>21.22</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>115.93</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDSHRI</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>1120.94</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1120.92</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1121.45</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>1121.46</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>MAXESTATES</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>560.79</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>535.6</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>568.9</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>MBECL</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>315.42</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>315.42</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>346.92</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>346.92</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>PAISALO</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>82.77</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>84.47</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>84.20999999999999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>PARSVNATH</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>926</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>825.3200000000001</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>995.95</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>RCOM</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>66.98</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>1055.43</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1055.41</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1055.95</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>1055.95</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SHEKHAWATI</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>18.42</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>20.32</v>
+        <v>21.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1076.59</v>
+        <v>1076.81</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1076.57</v>
+        <v>1076.79</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1077.02</v>
+        <v>1077.17</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1077.03</v>
+        <v>1077.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1079.27</v>
+        <v>21.42</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1079.24</v>
+        <v>21.42</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1079.68</v>
+        <v>22.27</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1079.68</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>20.93</v>
+        <v>2.39</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20.93</v>
+        <v>2.31</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>21.84</v>
+        <v>2.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.84</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.25</v>
+        <v>1077.85</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.25</v>
+        <v>1077.81</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2.33</v>
+        <v>1078.18</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2.33</v>
+        <v>1078.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1077.64</v>
+        <v>27.61</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1077.59</v>
+        <v>26.45</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1078.05</v>
+        <v>29.65</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1078.04</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42.87</v>
+        <v>1144.68</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>40.37</v>
+        <v>1144.64</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46.52</v>
+        <v>1145.02</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46.62</v>
+        <v>1145.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1144.46</v>
+        <v>1007.96</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1144.42</v>
+        <v>1007.92</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1144.88</v>
+        <v>1008.29</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1144.88</v>
+        <v>1008.29</v>
       </c>
     </row>
     <row r="11">
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1098.53</v>
+        <v>1098.74</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1098.38</v>
+        <v>1098.59</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1098.94</v>
+        <v>1099.06</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1098.95</v>
+        <v>1099.07</v>
       </c>
     </row>
     <row r="12">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
+        <v>115.92</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>115.9</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>115.88</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>115.93</v>
+        <v>115.95</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>115.95</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1121.17</v>
+        <v>1103.13</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1121.15</v>
+        <v>1103.11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1121.58</v>
+        <v>1103.47</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1121.58</v>
+        <v>1103.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>565.5599999999999</v>
+        <v>1121.39</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>538.75</v>
+        <v>1121.37</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>572.1</v>
+        <v>1121.72</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>571</v>
+        <v>1121.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>65.7</v>
+        <v>572</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>65.7</v>
+        <v>545.8200000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>68.31</v>
+        <v>577.6</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>68.31</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1055.66</v>
+        <v>45.58</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1055.64</v>
+        <v>43.07</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1056.07</v>
+        <v>51.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1056.09</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>NAGREEKCAP</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,16 +957,132 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>19.42</v>
+        <v>26.61</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>18.44</v>
+        <v>24.06</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.22</v>
+        <v>27.92</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.3</v>
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>QMSMEDI</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>163.17</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>155.84</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>168.92</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>168.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1321.26</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1224.52</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1357.2</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1351.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SANGINITA</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>69.67</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1055.87</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1055.85</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1056.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1056.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1076.81</v>
+        <v>1077.09</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1076.79</v>
+        <v>1077.06</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1077.17</v>
+        <v>1077.58</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1077.17</v>
+        <v>1077.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.42</v>
+        <v>843.71</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>21.42</v>
+        <v>814.04</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>22.27</v>
+        <v>845.75</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>22.27</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.39</v>
+        <v>629.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2.31</v>
+        <v>608.61</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.5</v>
+        <v>636.95</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.53</v>
+        <v>639.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.29</v>
+        <v>310.05</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2.29</v>
+        <v>307.66</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.37</v>
+        <v>317.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.37</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1077.85</v>
+        <v>100.74</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1077.81</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1078.18</v>
+        <v>107.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1078.19</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>DHARMAJ</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>27.61</v>
+        <v>275.21</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>26.45</v>
+        <v>266.99</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>29.65</v>
+        <v>276.15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>29.51</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.06</v>
+        <v>21.85</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.06</v>
+        <v>21.85</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.08</v>
+        <v>22.71</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.08</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1144.68</v>
+        <v>51.59</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1144.64</v>
+        <v>50.14</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1145.02</v>
+        <v>52.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1145.03</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1007.96</v>
+        <v>2.36</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1007.92</v>
+        <v>2.31</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1008.29</v>
+        <v>2.58</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1008.29</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1098.74</v>
+        <v>2.33</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1098.59</v>
+        <v>2.33</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1099.06</v>
+        <v>2.41</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1099.07</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>115.92</v>
+        <v>1078.12</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>115.9</v>
+        <v>1078.1</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>115.95</v>
+        <v>1078.63</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>115.96</v>
+        <v>1078.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1103.13</v>
+        <v>28.71</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1103.11</v>
+        <v>27.49</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1103.47</v>
+        <v>30.39</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1103.46</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>KIRLFER</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1121.39</v>
+        <v>475.79</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1121.37</v>
+        <v>465.06</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1121.72</v>
+        <v>480.65</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1121.72</v>
+        <v>483.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>572</v>
+        <v>0.06</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>545.8200000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>577.6</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>575</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>45.58</v>
+        <v>3.86</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>43.07</v>
+        <v>3.75</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>51.9</v>
+        <v>4.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>51.9</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKCAP</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26.61</v>
+        <v>1145.03</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>24.06</v>
+        <v>1144.88</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>27.92</v>
+        <v>1145.47</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>28.25</v>
+        <v>1145.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>163.17</v>
+        <v>1007.96</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>155.84</v>
+        <v>1007.92</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>168.92</v>
+        <v>1008.29</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>168.7</v>
+        <v>1008.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1321.26</v>
+        <v>1099.01</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1224.52</v>
+        <v>1098.86</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1357.2</v>
+        <v>1099.49</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1351.3</v>
+        <v>1099.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,45 +1044,393 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>67</v>
+        <v>115.95</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>67</v>
+        <v>115.93</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>69.67</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>69.67</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>LIQUIDPLUS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1103.41</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1103.39</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1103.91</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1103.92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1121.65</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1121.63</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1122.13</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1122.15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MAXESTATES</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>578.47</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>553.3099999999999</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>594</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>54.49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MONQ50</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>246.37</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>396.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>OILCOUNTUB</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>65.54000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>332.61</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>316.47</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>344.35</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>344.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>QMSMEDI</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>167.84</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>159.88</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>177.36</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>177.36</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1371.2</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1259.1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1374.3</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SANGINITA</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>71.06</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>71.06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>SBILIQETF</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>1055.87</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>1055.85</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>1056.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>1056.2</v>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1056.14</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1056.12</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1056.62</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1056.63</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SRD</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>39.16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>VETO</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>131.68</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>126.15</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>139.15</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>139.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1077.09</v>
+        <v>1077.28</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1077.06</v>
+        <v>1077.25</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1077.58</v>
+        <v>1077.73</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1077.57</v>
+        <v>1077.74</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>843.71</v>
+        <v>852.88</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>814.04</v>
+        <v>823.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>845.75</v>
+        <v>848.75</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>629.6</v>
+        <v>314.46</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>608.61</v>
+        <v>312.07</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>636.95</v>
+        <v>323.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>639.95</v>
+        <v>323.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>310.05</v>
+        <v>104.62</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>307.66</v>
+        <v>98.73</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>317.2</v>
+        <v>109.17</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>317.2</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>CCHHL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>100.74</v>
+        <v>12.98</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>94.68000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>107.62</v>
+        <v>13.02</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>107.62</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>275.21</v>
+        <v>22.28</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>266.99</v>
+        <v>22.28</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>276.15</v>
+        <v>23.16</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>277</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>21.85</v>
+        <v>54.42</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>21.85</v>
+        <v>51.24</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.71</v>
+        <v>61.49</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>22.71</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>51.59</v>
+        <v>2.45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>50.14</v>
+        <v>2.43</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>52.9</v>
+        <v>2.63</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>52.7</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.33</v>
+        <v>551.29</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.33</v>
+        <v>533.13</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.41</v>
+        <v>559.4</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.41</v>
+        <v>559.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1078.12</v>
+        <v>1109.36</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1078.1</v>
+        <v>1068.08</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1078.63</v>
+        <v>1130.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1078.63</v>
+        <v>1131.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28.71</v>
+        <v>0.06</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>27.49</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>30.39</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>30.6</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KIRLFER</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>475.79</v>
+        <v>4.02</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>465.06</v>
+        <v>3.97</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>480.65</v>
+        <v>4.4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>483.5</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.06</v>
+        <v>1008.24</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.06</v>
+        <v>1008.21</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.08</v>
+        <v>1008.83</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.08</v>
+        <v>1008.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.86</v>
+        <v>1099.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.75</v>
+        <v>1099.16</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4.2</v>
+        <v>1099.64</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.21</v>
+        <v>1099.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1145.03</v>
+        <v>115.97</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1144.88</v>
+        <v>115.95</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1145.47</v>
+        <v>116.01</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1145.48</v>
+        <v>116.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1007.96</v>
+        <v>1121.85</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1007.92</v>
+        <v>1121.83</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1008.29</v>
+        <v>1122.28</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1008.29</v>
+        <v>1122.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1099.01</v>
+        <v>589.47</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1098.86</v>
+        <v>562.33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1099.49</v>
+        <v>597.9</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1099.49</v>
+        <v>591.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>115.95</v>
+        <v>51.59</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>115.93</v>
+        <v>51.04</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>116</v>
+        <v>57.21</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>116</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1103.41</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1103.39</v>
+        <v>64.09</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1103.91</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1103.92</v>
+        <v>66.84999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1121.65</v>
+        <v>340.49</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1121.63</v>
+        <v>322.87</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1122.13</v>
+        <v>352.65</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1122.15</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>578.47</v>
+        <v>1295.7</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>553.3099999999999</v>
+        <v>1249.52</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>594</v>
+        <v>1349.3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>594</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>48.32</v>
+        <v>173.49</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46.8</v>
+        <v>165.98</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>54.49</v>
+        <v>186.22</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>54.49</v>
+        <v>186.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MONQ50</t>
+          <t>RRECL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>291</v>
+        <v>142.89</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>246.37</v>
+        <v>127.04</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>396.3</v>
+        <v>138.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>396.3</v>
+        <v>138.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>63.41</v>
+        <v>69.7</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>62.58</v>
+        <v>69.7</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>65.54000000000001</v>
+        <v>72.48</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>65.54000000000001</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>332.61</v>
+        <v>1056.33</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>316.47</v>
+        <v>1056.31</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>344.35</v>
+        <v>1056.76</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>344.25</v>
+        <v>1056.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>167.84</v>
+        <v>0.54</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>159.88</v>
+        <v>0.52</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>177.36</v>
+        <v>0.55</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>177.36</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>VETO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,132 +1305,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1371.2</v>
+        <v>135.46</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1259.1</v>
+        <v>129.37</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1374.3</v>
+        <v>143.78</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>71.06</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>71.06</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>1056.14</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1056.12</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>1056.62</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>1056.63</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SRD</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>40.03</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>38.64</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>39.15</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>39.16</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>VETO</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>131.68</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>126.15</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>139.15</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>139.15</v>
+        <v>142.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1077.28</v>
+        <v>491.42</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1077.25</v>
+        <v>475.11</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1077.73</v>
+        <v>491.35</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1077.74</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>852.88</v>
+        <v>660.0599999999999</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>823.2</v>
+        <v>637.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>848.75</v>
+        <v>656.4</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>846</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>ACSTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>314.46</v>
+        <v>67.23</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>312.07</v>
+        <v>65.17</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>323.5</v>
+        <v>76.56</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>323.5</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>104.62</v>
+        <v>517.0599999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>98.73</v>
+        <v>490.39</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>109.17</v>
+        <v>520.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>109.08</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CCHHL</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12.98</v>
+        <v>782.72</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.4</v>
+        <v>741.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>13.02</v>
+        <v>837.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>12.98</v>
+        <v>836.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>22.28</v>
+        <v>25.28</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>22.28</v>
+        <v>22.22</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.16</v>
+        <v>29.68</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>23.16</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>AJMERA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>54.42</v>
+        <v>118.01</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>51.24</v>
+        <v>113.34</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>61.49</v>
+        <v>120.63</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>60.1</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2.45</v>
+        <v>804.63</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2.43</v>
+        <v>773.42</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2.63</v>
+        <v>823.3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2.63</v>
+        <v>825.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.37</v>
+        <v>19.21</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.37</v>
+        <v>17.74</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.45</v>
+        <v>19.55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.45</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ALPHAETF</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>551.29</v>
+        <v>26.31</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>533.13</v>
+        <v>25.93</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>559.4</v>
+        <v>26.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>559.4</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>ALUFLUOR</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1109.36</v>
+        <v>534.09</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1068.08</v>
+        <v>503.47</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1130.5</v>
+        <v>577.55</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1131.1</v>
+        <v>581.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.06</v>
+        <v>1077.51</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.06</v>
+        <v>1077.48</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.08</v>
+        <v>1078.01</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.08</v>
+        <v>1078.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.02</v>
+        <v>8916.200000000001</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3.97</v>
+        <v>8769.700000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>4.4</v>
+        <v>9069</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4.41</v>
+        <v>9069</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>ARCHIDPLY</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1008.24</v>
+        <v>105.49</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1008.21</v>
+        <v>101.88</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1008.83</v>
+        <v>109.77</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1008.83</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>ARDEE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1099.2</v>
+        <v>50.1</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1099.16</v>
+        <v>48.44</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1099.64</v>
+        <v>52.25</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1099.64</v>
+        <v>52.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>ARIS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>115.97</v>
+        <v>135.45</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>115.95</v>
+        <v>126.91</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>116.01</v>
+        <v>143.72</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>116.02</v>
+        <v>143.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1121.85</v>
+        <v>653.09</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1121.83</v>
+        <v>625.59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1122.28</v>
+        <v>651.25</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1122.28</v>
+        <v>652</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>589.47</v>
+        <v>451.87</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>562.33</v>
+        <v>438.35</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>597.9</v>
+        <v>457.75</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>591.1</v>
+        <v>460.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>51.59</v>
+        <v>320.27</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>51.04</v>
+        <v>319.06</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>57.21</v>
+        <v>336.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>57.21</v>
+        <v>336.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>180.24</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>64.09</v>
+        <v>174.83</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>191.38</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>191.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>BELLACASA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>340.49</v>
+        <v>267.89</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>322.87</v>
+        <v>254.57</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>352.65</v>
+        <v>284.12</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>354</v>
+        <v>284.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1295.7</v>
+        <v>240.29</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1249.52</v>
+        <v>233.36</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1349.3</v>
+        <v>249.78</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1352</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>173.49</v>
+        <v>129.93</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>165.98</v>
+        <v>125.22</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>186.22</v>
+        <v>130.49</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>186.22</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RRECL</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>142.89</v>
+        <v>254.29</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>127.04</v>
+        <v>242.69</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>138.8</v>
+        <v>260.6</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>138.8</v>
+        <v>260.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>69.7</v>
+        <v>215.49</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>69.7</v>
+        <v>208.23</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>72.48</v>
+        <v>220.05</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>72.48</v>
+        <v>219.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1056.33</v>
+        <v>322.29</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1056.31</v>
+        <v>311.77</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1056.76</v>
+        <v>322.45</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1056.78</v>
+        <v>322.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.54</v>
+        <v>583.3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.52</v>
+        <v>565.48</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.55</v>
+        <v>585.75</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>584.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,16 +1305,4163 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>135.46</v>
+        <v>261.04</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>129.37</v>
+        <v>251.57</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>143.78</v>
+        <v>267.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>142.5</v>
+        <v>267.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BOSCH-HCIL</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1715.94</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1669.18</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2734.06</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2638.4</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2793.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CARBORUNIV</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1158.72</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1101.14</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1264.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1263.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>533.98</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>554.6</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CCHHL</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CHEMCON</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>213.93</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>228.66</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>227.15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CHEMPLASTS</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>171.62</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>85.59</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>125.82</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>125.82</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>DEEDEV</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>676.98</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>641.02</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>711.15</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1356.94</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1386.2</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>DEVYANI</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>141.55</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>137.52</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>140.11</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>139.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>653.7</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>637.1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>675</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>DPABHUSHAN</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1430.62</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1361.42</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1455.9</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1195.92</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1169.38</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1211.2</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1211.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>DSKULKARNI</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>23.16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ECOSMOBLTY</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>106.76</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>109.11</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>108.83</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>EDELWEISS</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>136.85</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>130.85</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>142.03</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>142.48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>EIEL</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>202.73</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>196.11</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>203.32</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>203.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>EMKAY</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>256.92</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>245.43</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ENGINERSIN</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>279.69</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>267.63</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>306.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>3196.54</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3093.82</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>3214.4</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>EPACKPEB</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>237.27</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>226.7</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>253.95</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>255.55</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>342.65</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>EVERESTIND</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>422.53</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>445.65</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>FEDDERSHOL</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>FLEXITUFF</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GALAPREC</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1057.62</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1006.12</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1164.2</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1173.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GCSL</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>624.77</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>597.9</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>642.7</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1448.06</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1410.6</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1483.8</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1483.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GREAVESCOT</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>198.03</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>189.84</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>206.01</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>206.65</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GRINDWELL</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1870.3</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1977.6</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GROWWRLTY</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GVKPIL</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GVPIL</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>660.21</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>633.24</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>686.3</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5378.4</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>5277.7</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>5394</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>5394</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HIKAL</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>233.11</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>232.43</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>351.48</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4944.6</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>4850.8</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>5028.5</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>5028.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>INDIGOPNTS</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1120.78</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1085.06</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1099.7</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1029.88</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1251.9</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>1251.65</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>INOXINDIA</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2107.92</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>2031.18</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2168.9</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>134.75</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>138.15</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>138.15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>IRISDOREME</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>813.39</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>776.8099999999999</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>867.85</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ITCHOTELS</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>158.18</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>154.22</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>161.23</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>161.61</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>IVZBANKNF</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>56.53</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>JGCHEM</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>613.61</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>585.4400000000001</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>621.55</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1144.54</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1114.86</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1175.3</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1175.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1275.98</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1254.24</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1297.8</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1297.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>KAMATHOTEL</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>230.86</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>219.63</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>240.35</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>239.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>KNAGRI</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>205.69</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>187.35</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>211.63</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>212.95</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>KROSS</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>253.42</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>235.53</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>278.56</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>279.41</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>KSHITIJ-RE</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>KSHITIJPOL</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>KUANTUM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>82.61</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>KUSUMGAR</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>596.7</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>566.6900000000001</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>635.1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1989.52</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>1935.16</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2034</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>559.74</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>531.25</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>577.55</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>575.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>LEAPIND</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>137.09</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>148.62</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDBETF</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1099.42</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1099.4</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>1099.91</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDCASE</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>115.98</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>116.04</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>116.04</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1122.07</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1122.05</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1122.57</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>1122.58</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>LLOYDSENGG</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>91.63</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>1136.9</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>1100.82</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>1162.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>84.11</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>MANINDS</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>877.8099999999999</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>814.58</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>986.7</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>1000.3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>MANIPALHOS</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>743.04</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>721.26</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>760.95</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>760.6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>MAPMYINDIA</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>909.66</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>883.22</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>906.8</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>401.73</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>438.69</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>438.69</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>MHRIL</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>200.58</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>193.82</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>201.39</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>202.15</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>290.68</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>277.23</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>317.25</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>317.25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MOREALTY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>87.69</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>MOTOUR</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>77.94</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>78.15000000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>NDRAUTO</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>726.02</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>699.67</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>763.15</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>NEXT50ADD</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>72.88</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>NEXT50BETA</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>77.91</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>NIF500BETA</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>36.78</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>NOCIL</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>186.45</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>206.3</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>206.19</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>NSLNISP</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>44.01</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>1732.42</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>OILCOUNTUB</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>OLECTRA</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>1219.36</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>1275.9</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>1278.9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>OMAXAUTO</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>189.03</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>174.62</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>209.94</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>209.94</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>OSWALPUMPS</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>282.76</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>272.75</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>284.1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>346.35</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>PDSL</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>361.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>PENIND</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>174.56</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>183.31</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>PENINLAND</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1926.88</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>1883.28</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>1993.2</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>1993.2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>POCL</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>476.87</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>456.38</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>488.7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>8358.6</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>8223.5</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>8417</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>8417</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>PRECAM</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>114.17</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>122.11</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>1471.14</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1437.12</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>QMSMEDI</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>171.19</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>195.1</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>195.69</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>RAILTEL</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>265.05</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>256.48</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>269.2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>211.23</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>203.18</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>221.86</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>221.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>RAMASTEEL</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>RBZJEWEL</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>174.06</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>163.55</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>178.05</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>RHIM</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>376.41</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>388.9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ROLEXRINGS</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>175.62</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>183.58</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>182.66</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>RUPA</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>137.85</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>133.53</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>140.63</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>140.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>RUSTOMJEE</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>344.13</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>368.9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SANGHVIMOV</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>430.96</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>415.57</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>441.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SANGINITA</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>75.39</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>4280.28</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>4091.8</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>4621.4</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SASKEN</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>1756.52</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>1697.66</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>1780.6</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>1056.56</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>1056.54</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>1057.04</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>1057.04</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SCODATUBES</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>125.03</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>138.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SEKURITIND</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>113.82</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>113.85</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SGRL</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>711.49</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>670.2</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>735.55</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SIGMAADV</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>889.42</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>832.26</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>936.7</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SMLMAH</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>6496.1</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>6234.4</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>6794</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>6808.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SMSPHARMA</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>448.88</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>426.92</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>482.95</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>SPLPETRO</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>852.54</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>815.29</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>882.2</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>881.8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>STLNETWORK</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>1164.06</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>1114.88</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>1199.6</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>1195.1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SUPRIYA</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>936.74</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>892.02</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1000.9</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SYSTMTXC</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>73.63</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>TANAA</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>279.89</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>349.6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>612.27</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>574.48</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>692.45</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>TEXRAIL</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>116.91</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>111.82</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>124.8</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>569.96</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>541.04</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>601.5</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>602.4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>TIMETECHNO</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>180.21</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>175.78</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>181.96</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>182.25</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>441.24</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>428.74</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>450.3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>4935.1</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>4821.9</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>4985</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>4985</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>TOYAMSL</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>UNIMECH</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1652.5</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>1561.8</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>1716.1</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>VAML</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>421.65</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>409.66</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>436.3</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>425.81</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>417.23</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>436.15</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>436.15</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>VENUSREM</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>1611.82</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>1535.28</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>1643.7</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>VISHNU</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>721.08</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>698.48</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>723.95</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>VSTTILLERS</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>4286.04</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>4103.4</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>4425</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>2653.8</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>2506.02</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>2796.8</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>2796.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>217.14</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>208.69</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>223.77</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>223.5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>WESTLIFE</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>571.96</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>547.74</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>598.7</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>602.05</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>2171.88</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>2061.64</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>2329.7</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ZODIACLOTH</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>69.67</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ZOTA</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>1229.38</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>1160.22</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1390.6</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ZUARI</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>221.17</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>213.88</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>224.09</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>223.49</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>1153.8</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>1128.38</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>1170.1</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>1170.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>673.46</v>
+        <v>692.74</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>643.41</v>
+        <v>657.1799999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>712.15</v>
+        <v>715.05</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>722</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>527.26</v>
+        <v>20.12</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>502.02</v>
+        <v>18.79</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>527.2</v>
+        <v>21.38</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>527.55</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>19.59</v>
+        <v>1078.02</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18.25</v>
+        <v>1077.99</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19.86</v>
+        <v>1078.58</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>20.05</v>
+        <v>1078.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1077.74</v>
+        <v>334.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1077.71</v>
+        <v>334.09</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1078.16</v>
+        <v>350.05</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1078.17</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>327.11</v>
+        <v>1766.04</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>326.08</v>
+        <v>1702.28</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>343.2</v>
+        <v>1811.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>343.2</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1736.94</v>
+        <v>1080.71</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1687.86</v>
+        <v>1080.4</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1730</v>
+        <v>1081.27</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1728.1</v>
+        <v>1081.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1221.4</v>
+        <v>118.49</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1148.94</v>
+        <v>106.95</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1296.5</v>
+        <v>152.24</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1285</v>
+        <v>152.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>226.61</v>
+        <v>68.91</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>218.15</v>
+        <v>62.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>228.08</v>
+        <v>76.84</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>226.25</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>105.02</v>
+        <v>297.39</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>95.86</v>
+        <v>281.46</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>138.4</v>
+        <v>305.35</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>138.4</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>99.44</v>
+        <v>23.17</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>95.28</v>
+        <v>23.17</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>100.22</v>
+        <v>24.09</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DEEPAKFERT</t>
+          <t>EASTSILK</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1371.94</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1333.06</v>
+        <v>64.86</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1361.4</v>
+        <v>72</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1360</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>EKI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>64.69</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>59.85</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>72.68000000000001</v>
+        <v>100.99</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>72.2</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>288.86</v>
+        <v>41.24</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>274.81</v>
+        <v>39.11</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>295.05</v>
+        <v>42.86</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>293.4</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>22.72</v>
+        <v>1484.02</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>22.72</v>
+        <v>1448.14</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.62</v>
+        <v>1497.2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.62</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EKI</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>618.46</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>70.75</v>
+        <v>597.26</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>630.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GALAPREC</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1090.16</v>
+        <v>44.64</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1034.52</v>
+        <v>42.76</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1117.1</v>
+        <v>48.51</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1114.2</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1025.56</v>
+        <v>213.79</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>980.96</v>
+        <v>201.21</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1014</v>
+        <v>234.78</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1009</v>
+        <v>234.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>HERANBA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1468.76</v>
+        <v>176.95</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1432.04</v>
+        <v>167.32</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1482.6</v>
+        <v>187.6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1480</v>
+        <v>189.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>INDOMIM</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>42.75</v>
+        <v>1236.77</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>41.13</v>
+        <v>1155.92</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>42.39</v>
+        <v>1275.95</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>42.8</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>205.19</v>
+        <v>134.66</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>194.54</v>
+        <v>127.91</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>221.83</v>
+        <v>138.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>222.25</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1963.02</v>
+        <v>753.4299999999999</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1898</v>
+        <v>703.49</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1981</v>
+        <v>846.4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1994.9</v>
+        <v>846.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.47</v>
+        <v>761.02</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.47</v>
+        <v>712.3099999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.58</v>
+        <v>804.55</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.58</v>
+        <v>814</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HEALTHADD</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>16.96</v>
+        <v>0.06</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>16.75</v>
+        <v>0.06</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>16.96</v>
+        <v>0.08</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>16.91</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HERANBA</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>170.42</v>
+        <v>1099.92</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>165.78</v>
+        <v>1099.9</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>172.27</v>
+        <v>1100.48</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>172.9</v>
+        <v>1100.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1168.57</v>
+        <v>116.05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1092.14</v>
+        <v>116.03</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1311.15</v>
+        <v>116.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1314.45</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>160.47</v>
+        <v>1122.58</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>156.02</v>
+        <v>1122.56</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>164.01</v>
+        <v>1123.13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>163.52</v>
+        <v>1123.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>713.75</v>
+        <v>74.75</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>666.8</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>806.1</v>
+        <v>79.67</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>806.1</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>209.37</v>
+        <v>433.16</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>196.25</v>
+        <v>433.16</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>213.63</v>
+        <v>456.4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>209.99</v>
+        <v>456.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.06</v>
+        <v>57.66</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.06</v>
+        <v>54.61</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.08</v>
+        <v>60.46</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.08</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4.51</v>
+        <v>2.92</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.06</v>
+        <v>2.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.07</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2012.5</v>
+        <v>618.77</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1966.46</v>
+        <v>566.64</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2026.2</v>
+        <v>690.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2026.2</v>
+        <v>695</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1099.64</v>
+        <v>1057.06</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1099.62</v>
+        <v>1057.04</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1100.05</v>
+        <v>1057.62</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1100.05</v>
+        <v>1057.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>116.02</v>
+        <v>6.28</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>116</v>
+        <v>5.91</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>116.06</v>
+        <v>6.51</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>116.06</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1122.3</v>
+        <v>228.18</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1122.28</v>
+        <v>219.67</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1122.71</v>
+        <v>239.46</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1122.72</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>87.02</v>
+        <v>48.91</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>83.31</v>
+        <v>47.59</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>90.91</v>
+        <v>54.61</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>90.8</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>72.18000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>68.75</v>
+        <v>10.63</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>75.58</v>
+        <v>12.18</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>75.29000000000001</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>337.45</v>
+        <v>385.93</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>323.99</v>
+        <v>365.94</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>337.4</v>
+        <v>410.65</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>336.9</v>
+        <v>407.15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>418.37</v>
+        <v>123.28</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>418.37</v>
+        <v>117.73</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>447.46</v>
+        <v>125.67</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>447.46</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NDRAUTO</t>
+          <t>TGVSL</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>746.74</v>
+        <v>112.1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>718.71</v>
+        <v>105.65</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>754.2</v>
+        <v>124.78</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>756</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>VASCONEQ</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>153.27</v>
+        <v>34.02</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>147.33</v>
+        <v>31.44</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>165</v>
+        <v>34.76</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>165</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>197.97</v>
+        <v>835.27</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>181.65</v>
+        <v>758.76</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>201.62</v>
+        <v>918.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>199.9</v>
+        <v>903.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,480 +1711,16 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>56.24</v>
+        <v>1183</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>53.33</v>
+        <v>1159.96</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>59.15</v>
+        <v>1203.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>59.47</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>PRITIKAUTO</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>17.14</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>RELIABLE</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>143.61</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>138.17</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>147.95</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>147.8</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>1056.78</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1056.76</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>1057.19</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>1057.2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>818.09</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>790.38</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>816.3</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>816.3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>46.17</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>44.96</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>52.18</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SUNFLAG</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>371.39</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>354.45</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>SUPRIYA</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>960.79</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>913.92</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>961.75</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>SYSTMTXC</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>75.31</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>79.05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TEXRAIL</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>120.07</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>114.68</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>126.77</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>126.9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TIRUPATIFL</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>73.27</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>79.87</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>4963.1</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>4851.2</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>4928.5</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>4928.5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>VASCONEQ</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>30.49</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>33.31</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>VIPCLOTHNG</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>21.52</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>21.74</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>VSTTILLERS</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>4400.28</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>4187.66</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>4516.7</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>4436</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>WEWIN</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>45.56</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>42.61</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>49.48</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>1169.26</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>1143.5</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>1180.3</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>1180.3</v>
+        <v>1203.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>692.74</v>
+        <v>35.07</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>657.1799999999999</v>
+        <v>32.11</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>715.05</v>
+        <v>35.28</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>714.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.12</v>
+        <v>250.09</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18.79</v>
+        <v>239.16</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.38</v>
+        <v>260.1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>21.25</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1078.02</v>
+        <v>20.65</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1077.99</v>
+        <v>19.34</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1078.58</v>
+        <v>21.09</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1078.59</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>334.09</v>
+        <v>1078.25</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>334.09</v>
+        <v>1078.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>350.05</v>
+        <v>1078.72</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>350.05</v>
+        <v>1078.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1766.04</v>
+        <v>342.06</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1702.28</v>
+        <v>342.06</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1811.6</v>
+        <v>357.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1823</v>
+        <v>357.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>BLUECLOUDS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1080.71</v>
+        <v>21.52</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1080.4</v>
+        <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1081.27</v>
+        <v>21.71</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1081.27</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>118.49</v>
+        <v>1798.12</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>106.95</v>
+        <v>1727.9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>152.24</v>
+        <v>1802.4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>152.24</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>68.91</v>
+        <v>134.58</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>62.86</v>
+        <v>121.09</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>76.84</v>
+        <v>167.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>76.8</v>
+        <v>167.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>297.39</v>
+        <v>5.88</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>281.46</v>
+        <v>5.79</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>305.35</v>
+        <v>6.51</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>306</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.17</v>
+        <v>73.34</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>23.17</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>24.09</v>
+        <v>72.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>24.09</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.43000000000001</v>
+        <v>303.76</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>64.86</v>
+        <v>289.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>72</v>
+        <v>302.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>72</v>
+        <v>303.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EKI</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>86.26000000000001</v>
+        <v>23.63</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>76.56999999999999</v>
+        <v>23.63</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>100.99</v>
+        <v>24.57</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>101.22</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="14">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>41.24</v>
+        <v>42.34</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>39.11</v>
+        <v>39.96</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>42.86</v>
+        <v>43</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>42.86</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="15">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1484.02</v>
+        <v>1509.66</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1448.14</v>
+        <v>1463.42</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1497.2</v>
+        <v>1533.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1500</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>618.46</v>
+        <v>221.33</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>597.26</v>
+        <v>208.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>630.3</v>
+        <v>230.4</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>632</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>44.64</v>
+        <v>1079.29</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.76</v>
+        <v>1079.24</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>48.51</v>
+        <v>1079.76</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>48.59</v>
+        <v>1079.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>HITECHGEAR</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>213.79</v>
+        <v>593.1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>201.21</v>
+        <v>569.59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>234.78</v>
+        <v>648.85</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>234.52</v>
+        <v>649.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HERANBA</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>176.95</v>
+        <v>85.03</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>167.32</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>187.6</v>
+        <v>83.05</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>189.46</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1236.77</v>
+        <v>137.26</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1155.92</v>
+        <v>130.43</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1275.95</v>
+        <v>139.68</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1271</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>134.66</v>
+        <v>793.17</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>127.91</v>
+        <v>743.55</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>138.2</v>
+        <v>863.15</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>138</v>
+        <v>855.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>753.4299999999999</v>
+        <v>197.45</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>703.49</v>
+        <v>186.74</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>846.4</v>
+        <v>216.9</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>846.4</v>
+        <v>216.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>761.02</v>
+        <v>0.06</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>712.3099999999999</v>
+        <v>0.06</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>804.55</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>814</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.06</v>
+        <v>1720.9</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.06</v>
+        <v>1676.76</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.08</v>
+        <v>1730.7</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.08</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="25">
@@ -1189,16 +1189,16 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1099.92</v>
+        <v>1100.47</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1099.9</v>
+        <v>1100.13</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1100.48</v>
+        <v>1100.63</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1100.49</v>
+        <v>1100.63</v>
       </c>
     </row>
     <row r="26">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>116.05</v>
+        <v>116.08</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>116.03</v>
+        <v>116.06</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>116.1</v>
+        <v>116.11</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>116.11</v>
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1122.58</v>
+        <v>1122.81</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1122.56</v>
+        <v>1122.79</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1123.13</v>
+        <v>1123.27</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1123.14</v>
+        <v>1123.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>74.75</v>
+        <v>445.95</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>70.31999999999999</v>
+        <v>445.95</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>79.67</v>
+        <v>465.52</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>79.59</v>
+        <v>465.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>433.16</v>
+        <v>13.62</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>433.16</v>
+        <v>13.48</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>456.4</v>
+        <v>15.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>456.4</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>57.66</v>
+        <v>1301.06</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>54.61</v>
+        <v>1229.78</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>60.46</v>
+        <v>1296.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>60.85</v>
+        <v>1291.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.92</v>
+        <v>663.5700000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2.68</v>
+        <v>604.1799999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2.8</v>
+        <v>691.5</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.8</v>
+        <v>686.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>RAJTV</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>618.77</v>
+        <v>10.19</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>566.64</v>
+        <v>9.76</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>690.7</v>
+        <v>11.14</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>695</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="33">
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1057.06</v>
+        <v>1057.28</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1057.04</v>
+        <v>1057.26</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1057.62</v>
+        <v>1057.74</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1057.62</v>
+        <v>1057.75</v>
       </c>
     </row>
     <row r="34">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>6.28</v>
+        <v>6.42</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5.91</v>
+        <v>6.06</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>6.51</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>6.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>228.18</v>
+        <v>405.47</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>219.67</v>
+        <v>379.81</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>239.46</v>
+        <v>449.2</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>239</v>
+        <v>451.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>48.91</v>
+        <v>7.84</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>47.59</v>
+        <v>7.32</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>54.61</v>
+        <v>7.86</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>54.61</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>10.9</v>
+        <v>322.09</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>10.63</v>
+        <v>307.29</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>12.18</v>
+        <v>355.45</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>12.18</v>
+        <v>355.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>TGVSL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>385.93</v>
+        <v>117.5</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>365.94</v>
+        <v>109.43</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>410.65</v>
+        <v>121.88</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>407.15</v>
+        <v>121.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,132 +1595,16 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>123.28</v>
+        <v>1195.26</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>117.73</v>
+        <v>1170.66</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>125.67</v>
+        <v>1215</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>125.5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TGVSL</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>105.65</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>124.78</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>VASCONEQ</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>34.78</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>WHIRLPOOL</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>835.27</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>758.76</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>918.9</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>903.55</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1183</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1159.96</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1203.9</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1203.9</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.07</v>
+        <v>1078.48</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>32.11</v>
+        <v>1078.46</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>35.28</v>
+        <v>1078.86</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36</v>
+        <v>1078.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>250.09</v>
+        <v>350.19</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>239.16</v>
+        <v>350.19</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>260.1</v>
+        <v>364.15</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>260.75</v>
+        <v>364.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>20.65</v>
+        <v>151.95</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19.34</v>
+        <v>136.59</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>21.09</v>
+        <v>175.74</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.42</v>
+        <v>175.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1078.25</v>
+        <v>6.18</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1078.22</v>
+        <v>6.18</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1078.72</v>
+        <v>6.64</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1078.74</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>342.06</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>342.06</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>357.05</v>
+        <v>78.69</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>357.05</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>21.52</v>
+        <v>24.1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19.9</v>
+        <v>24.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>21.71</v>
+        <v>25.06</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>21.6</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1798.12</v>
+        <v>671.75</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1727.9</v>
+        <v>650.59</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1802.4</v>
+        <v>674.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1798</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>134.58</v>
+        <v>1528.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>121.09</v>
+        <v>1481.84</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>167.46</v>
+        <v>1537.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>167.46</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5.88</v>
+        <v>990.58</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5.79</v>
+        <v>937.92</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6.51</v>
+        <v>1010.35</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6.51</v>
+        <v>1013.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>73.34</v>
+        <v>207.39</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>65.81999999999999</v>
+        <v>194.72</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>72.2</v>
+        <v>217.04</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>72.45</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>303.76</v>
+        <v>0.06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>289.2</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>302.8</v>
+        <v>0.08</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>303.95</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>23.63</v>
+        <v>116.1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>23.63</v>
+        <v>116.08</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>24.57</v>
+        <v>116.12</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>24.57</v>
+        <v>116.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>42.34</v>
+        <v>1105.91</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>39.96</v>
+        <v>1104.74</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>43</v>
+        <v>1105.23</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>43.02</v>
+        <v>1105.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1509.66</v>
+        <v>1123.03</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1463.42</v>
+        <v>1123.01</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1533.4</v>
+        <v>1123.41</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1534</v>
+        <v>1123.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>221.33</v>
+        <v>456.58</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>208.67</v>
+        <v>456.08</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>230.4</v>
+        <v>474.83</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>230.5</v>
+        <v>474.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1079.29</v>
+        <v>3603.44</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1079.24</v>
+        <v>3499.94</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1079.76</v>
+        <v>3605.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1079.76</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>593.1</v>
+        <v>1057.5</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>569.59</v>
+        <v>1057.48</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>648.85</v>
+        <v>1057.87</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>649.25</v>
+        <v>1057.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>85.03</v>
+        <v>3433.2</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>80.04000000000001</v>
+        <v>3214</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>83.05</v>
+        <v>3485.6</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>83.02</v>
+        <v>3494.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>137.26</v>
+        <v>427.75</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>130.43</v>
+        <v>397.76</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>139.68</v>
+        <v>464.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>139</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,538 +1073,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>793.17</v>
+        <v>339.39</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>743.55</v>
+        <v>325.29</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>863.15</v>
+        <v>373.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>855.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>KRONOX</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>197.45</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>186.74</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>216.9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>KSHITIJ-RE</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>LGEINDIA</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>1720.9</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1676.76</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1730.7</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDBETF</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1100.47</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1100.13</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>1100.63</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>1100.63</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDCASE</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>116.08</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>116.06</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>116.11</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>116.11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDSHRI</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>1122.81</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>1122.79</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1123.27</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>1123.29</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>MBECL</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>445.95</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>445.95</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>465.52</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>465.52</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>NEUEON</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>PGIL</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1301.06</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>1229.78</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1296.1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1291.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>PROTEAN</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>663.5700000000001</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>604.1799999999999</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>691.5</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>686.15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>RAJTV</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>11.28</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>1057.28</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1057.26</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1057.74</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>1057.75</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SIKKO</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>6.51</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SUNFLAG</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>405.47</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>379.81</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>449.2</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>451.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SWARAJ</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>322.09</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>307.29</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>355.45</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>355.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TGVSL</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>109.43</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>121.88</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>121.36</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>1195.26</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>1170.66</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>1215</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1215</v>
+        <v>373.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1078.48</v>
+        <v>1078.68</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1078.46</v>
+        <v>1078.66</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1078.86</v>
+        <v>1079</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1078.86</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>350.19</v>
+        <v>357.17</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>350.19</v>
+        <v>357.16</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>364.15</v>
+        <v>371.35</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>364.15</v>
+        <v>371.35</v>
       </c>
     </row>
     <row r="4">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>151.95</v>
+        <v>163.59</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>136.59</v>
+        <v>146.58</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>175.74</v>
+        <v>174.84</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>175.83</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.18</v>
+        <v>124.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6.18</v>
+        <v>117.65</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6.64</v>
+        <v>126.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>6.64</v>
+        <v>125.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>76.84999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>68.34999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>78.69</v>
+        <v>6.77</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>78.2</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>24.1</v>
+        <v>80.63</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24.1</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25.06</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>25.06</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>671.75</v>
+        <v>24.58</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>650.59</v>
+        <v>24.58</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>674.7</v>
+        <v>25.56</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>680</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1528.5</v>
+        <v>1049.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1481.84</v>
+        <v>1048.61</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1537.8</v>
+        <v>1049.84</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1545</v>
+        <v>1049.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>990.58</v>
+        <v>2.87</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>937.92</v>
+        <v>2.86</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1010.35</v>
+        <v>2.97</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1013.5</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>207.39</v>
+        <v>1547.28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>194.72</v>
+        <v>1497.64</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>217.04</v>
+        <v>1560</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>217</v>
+        <v>1561.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>GILLANDERS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.06</v>
+        <v>112.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.06</v>
+        <v>105.46</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.08</v>
+        <v>114.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.08</v>
+        <v>114.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>116.1</v>
+        <v>110.93</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>116.08</v>
+        <v>110.85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>116.12</v>
+        <v>110.95</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>116.13</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1105.91</v>
+        <v>6823.4</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1104.74</v>
+        <v>6519.9</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1105.23</v>
+        <v>7015.5</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1105.25</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1123.03</v>
+        <v>30.46</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1123.01</v>
+        <v>29.09</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1123.41</v>
+        <v>35.05</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1123.42</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>456.58</v>
+        <v>0.06</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>456.08</v>
+        <v>0.06</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>474.83</v>
+        <v>0.08</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>474.83</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3603.44</v>
+        <v>116.12</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3499.94</v>
+        <v>116.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3605.5</v>
+        <v>116.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3590</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1057.5</v>
+        <v>1123.23</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1057.48</v>
+        <v>1123.21</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1057.87</v>
+        <v>1123.55</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1057.87</v>
+        <v>1123.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3433.2</v>
+        <v>465.71</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3214</v>
+        <v>465.2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3485.6</v>
+        <v>484.32</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3494.1</v>
+        <v>484.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,45 +1044,306 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>427.75</v>
+        <v>175.16</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>397.76</v>
+        <v>166.44</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>464.3</v>
+        <v>179.21</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>465</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>OILCOUNTUB</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>76.61</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>76.61</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RAMRAT</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>581.35</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>557.9400000000001</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>582.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>579.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1057.7</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1057.68</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1058.02</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1058.02</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SHEKHAWATI</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>31.68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>757.2</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>739.08</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>770.4</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>766.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3641.16</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>3399.62</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>3846.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>443.84</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>415.97</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>456.05</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>452.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>SWARAJ</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>339.39</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>325.29</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>373.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>373.2</v>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>356.33</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>340.28</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>390.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TIMETECHNO</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>179.67</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>182.36</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>182.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1078.68</v>
+        <v>1078.96</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1078.66</v>
+        <v>1078.94</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1079</v>
+        <v>1079.57</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1079</v>
+        <v>1079.59</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>357.17</v>
+        <v>364.28</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>357.16</v>
+        <v>364.27</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>371.35</v>
+        <v>378.75</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>371.35</v>
+        <v>378.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>163.59</v>
+        <v>6.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>146.58</v>
+        <v>6.6</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>174.84</v>
+        <v>6.9</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>177.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>124.09</v>
+        <v>25.07</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>117.65</v>
+        <v>25.07</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>126.1</v>
+        <v>26.07</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>125.98</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6.41</v>
+        <v>1049.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6.41</v>
+        <v>1049.77</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.77</v>
+        <v>1050.39</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6.77</v>
+        <v>1050.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.63</v>
+        <v>2.92</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>71.70999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>80.51000000000001</v>
+        <v>3.02</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>80.73999999999999</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24.58</v>
+        <v>672.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>24.58</v>
+        <v>655.45</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>25.56</v>
+        <v>679.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25.56</v>
+        <v>680.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1049.5</v>
+        <v>10.84</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1048.61</v>
+        <v>9.43</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1049.84</v>
+        <v>11.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1049.85</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.87</v>
+        <v>0.06</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.86</v>
+        <v>0.06</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.97</v>
+        <v>0.08</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.97</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1547.28</v>
+        <v>1009.71</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1497.64</v>
+        <v>1008.64</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1560</v>
+        <v>1010.57</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1561.2</v>
+        <v>1010.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GILLANDERS</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>112.31</v>
+        <v>116.15</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>105.46</v>
+        <v>116.13</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>114.8</v>
+        <v>116.2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>114.49</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>110.93</v>
+        <v>1123.51</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>110.85</v>
+        <v>1123.49</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>110.95</v>
+        <v>1124.12</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>110.95</v>
+        <v>1124.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6823.4</v>
+        <v>475.01</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>6519.9</v>
+        <v>474.51</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>7015.5</v>
+        <v>494</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7000</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30.46</v>
+        <v>75.14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>29.09</v>
+        <v>74.88</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>35.05</v>
+        <v>78.14</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>35.05</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.06</v>
+        <v>2.05</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.06</v>
+        <v>2.05</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.08</v>
+        <v>2.13</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.08</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>116.12</v>
+        <v>27.94</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>116.1</v>
+        <v>26.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>116.15</v>
+        <v>34.93</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>116.15</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1123.23</v>
+        <v>1057.98</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1123.21</v>
+        <v>1057.96</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1123.55</v>
+        <v>1058.58</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1123.56</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>465.71</v>
+        <v>61.8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>465.2</v>
+        <v>58.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>484.32</v>
+        <v>61.8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>484.32</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>175.16</v>
+        <v>3761.36</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>166.44</v>
+        <v>3514.82</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>179.21</v>
+        <v>3853.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>179.95</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>73.69</v>
+        <v>370.83</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>73.06999999999999</v>
+        <v>353.46</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>76.61</v>
+        <v>377.55</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>76.61</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.02</v>
+        <v>1139.09</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2.01</v>
+        <v>1066.17</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2.09</v>
+        <v>1198</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2.09</v>
+        <v>1197.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>581.35</v>
+        <v>7.09</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>557.9400000000001</v>
+        <v>6.94</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>582.4</v>
+        <v>7.79</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>579.5</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,190 +1160,16 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1057.7</v>
+        <v>20.99</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1057.68</v>
+        <v>20.32</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1058.02</v>
+        <v>22.86</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1058.02</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SHEKHAWATI</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>31.68</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SHREEJISPG</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>757.2</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>739.08</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>770.4</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>766.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>3641.16</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>3399.62</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>3846.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>3850</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SUNFLAG</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>443.84</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>415.97</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>456.05</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>452.65</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SWARAJ</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>356.33</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>340.28</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>388.6</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>390.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TIMETECHNO</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>184.7</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>179.67</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>182.36</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>182.8</v>
+        <v>22.89</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1078.96</v>
+        <v>14.92</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1078.94</v>
+        <v>14.74</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1079.57</v>
+        <v>16.12</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1079.59</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>364.28</v>
+        <v>1079.19</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>364.27</v>
+        <v>1079.17</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>378.75</v>
+        <v>1079.71</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>378.75</v>
+        <v>1079.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.6</v>
+        <v>2198.88</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6.6</v>
+        <v>2062.82</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>6.9</v>
+        <v>2282.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6.9</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>25.07</v>
+        <v>371.53</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>25.07</v>
+        <v>371.52</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.07</v>
+        <v>386.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>26.07</v>
+        <v>386.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1049.79</v>
+        <v>1082.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1049.77</v>
+        <v>1081.38</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1050.39</v>
+        <v>1082.41</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1050.38</v>
+        <v>1082.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.92</v>
+        <v>6.77</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.92</v>
+        <v>6.77</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.02</v>
+        <v>7.03</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3.02</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>672.6</v>
+        <v>1801.98</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>655.45</v>
+        <v>1610.94</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>679.9</v>
+        <v>2130.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>680.1</v>
+        <v>2166.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10.84</v>
+        <v>25.57</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>9.43</v>
+        <v>25.57</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>11.7</v>
+        <v>26.59</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>11.65</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.06</v>
+        <v>1050.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.06</v>
+        <v>1049.99</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.08</v>
+        <v>1050.52</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.08</v>
+        <v>1050.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1009.71</v>
+        <v>2.97</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1008.64</v>
+        <v>2.96</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1010.57</v>
+        <v>3.07</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1010.57</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>116.15</v>
+        <v>679.3</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>116.13</v>
+        <v>664.17</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>116.2</v>
+        <v>681.75</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>116.22</v>
+        <v>683.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1123.51</v>
+        <v>2.27</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1123.49</v>
+        <v>2.19</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1124.12</v>
+        <v>2.47</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1124.13</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>475.01</v>
+        <v>32.87</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>474.51</v>
+        <v>32.37</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>494</v>
+        <v>37.67</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>494</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>75.14</v>
+        <v>129.22</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>74.88</v>
+        <v>123.03</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>78.14</v>
+        <v>127.98</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>78.14</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.05</v>
+        <v>371.46</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.05</v>
+        <v>351.02</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.13</v>
+        <v>379.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.13</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>27.94</v>
+        <v>0.06</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>26.8</v>
+        <v>0.06</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>34.93</v>
+        <v>0.08</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>34.93</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1057.98</v>
+        <v>1057.68</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1057.96</v>
+        <v>1057.13</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1058.58</v>
+        <v>1058.17</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1058.59</v>
+        <v>1058.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>61.8</v>
+        <v>1009.71</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>58.47</v>
+        <v>1008.64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>61.8</v>
+        <v>1010.57</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>62</v>
+        <v>1010.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3761.36</v>
+        <v>116.18</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3514.82</v>
+        <v>116.16</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3853.4</v>
+        <v>116.22</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3867</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>370.83</v>
+        <v>1123.74</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>353.46</v>
+        <v>1123.72</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>377.55</v>
+        <v>1124.28</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>375</v>
+        <v>1124.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SYMBIOTEC</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1139.09</v>
+        <v>484.5</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1066.17</v>
+        <v>484</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1198</v>
+        <v>503.85</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1197.3</v>
+        <v>503.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,45 +1131,393 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.09</v>
+        <v>22.89</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.94</v>
+        <v>21.58</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.79</v>
+        <v>23.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.79</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>MOLDTECH</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>209.22</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>200.16</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>213.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1727.66</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1645.04</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1820.8</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>OILCOUNTUB</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ONELIFECAP</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>43.52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1429.82</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1607.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SAPPL</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>286.84</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>320.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1058.21</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1058.19</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1058.76</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1058.77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1252.68</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1201.96</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1268.1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1281.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>801.35</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>752.84</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>812.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>814.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TICL</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>UYFINCORP</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>22.89</v>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>14.92</v>
+        <v>15.48</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>14.74</v>
+        <v>15.41</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>16.12</v>
+        <v>16.92</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>16.12</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1079.19</v>
+        <v>1295.14</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1079.17</v>
+        <v>1256.28</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1079.71</v>
+        <v>1313</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1079.73</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2198.88</v>
+        <v>715.76</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2062.82</v>
+        <v>681.49</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2282.3</v>
+        <v>753.7</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2280</v>
+        <v>762.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>371.53</v>
+        <v>1079.42</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>371.52</v>
+        <v>1079.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>386.3</v>
+        <v>1079.86</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>386.3</v>
+        <v>1079.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1082.4</v>
+        <v>378.92</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1081.38</v>
+        <v>378.71</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1082.41</v>
+        <v>394</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1082.4</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6.77</v>
+        <v>6.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.77</v>
+        <v>6.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7.03</v>
+        <v>7.17</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7.03</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1801.98</v>
+        <v>26.08</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1610.94</v>
+        <v>26.08</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2130.5</v>
+        <v>27.12</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2166.2</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>25.57</v>
+        <v>13915.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>25.57</v>
+        <v>13398.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>26.59</v>
+        <v>14279</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>26.59</v>
+        <v>14318</v>
       </c>
     </row>
     <row r="10">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1050.01</v>
+        <v>1050.24</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1049.99</v>
+        <v>1050.22</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1050.52</v>
+        <v>1050.67</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1050.53</v>
+        <v>1050.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.97</v>
+        <v>477.72</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.96</v>
+        <v>439.31</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.07</v>
+        <v>515.95</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.07</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>679.3</v>
+        <v>3.02</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>664.17</v>
+        <v>3.01</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>681.75</v>
+        <v>3.13</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>683.8</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.27</v>
+        <v>684.45</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.19</v>
+        <v>670.67</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.47</v>
+        <v>693.05</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2.47</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>32.87</v>
+        <v>304.87</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>32.37</v>
+        <v>291.48</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>37.67</v>
+        <v>315.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.67</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>129.22</v>
+        <v>238.93</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>123.03</v>
+        <v>228.62</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>127.98</v>
+        <v>262.78</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>128</v>
+        <v>262.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>371.46</v>
+        <v>35.27</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>351.02</v>
+        <v>33.58</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>379.2</v>
+        <v>38.78</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>380</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.06</v>
+        <v>211.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.06</v>
+        <v>202.08</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.08</v>
+        <v>214.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.08</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1057.68</v>
+        <v>0.06</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1057.13</v>
+        <v>0.06</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1058.17</v>
+        <v>0.08</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1058.16</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1009.71</v>
+        <v>1057.89</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1008.64</v>
+        <v>1057.84</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1010.57</v>
+        <v>1058.31</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1010.57</v>
+        <v>1058.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>116.18</v>
+        <v>1010.06</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>116.16</v>
+        <v>1010.06</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>116.22</v>
+        <v>1010.85</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>116.23</v>
+        <v>1010.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1123.74</v>
+        <v>116.2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1123.72</v>
+        <v>116.18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1124.28</v>
+        <v>116.23</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1124.28</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>484.5</v>
+        <v>1123.96</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>484</v>
+        <v>1123.94</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>503.85</v>
+        <v>1124.42</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>503.85</v>
+        <v>1124.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>22.89</v>
+        <v>410.16</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>21.58</v>
+        <v>369.15</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>23.9</v>
+        <v>455.7</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>24.2</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>MASPTOP50</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>209.22</v>
+        <v>106.55</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>200.16</v>
+        <v>100.29</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>213.5</v>
+        <v>111.05</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>213.5</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1727.66</v>
+        <v>23.59</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1645.04</v>
+        <v>22.11</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1820.8</v>
+        <v>25.05</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1810</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>76.64</v>
+        <v>212.22</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>76.64</v>
+        <v>204.56</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>79.7</v>
+        <v>216.72</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>79.7</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>40.64</v>
+        <v>133.79</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>38.68</v>
+        <v>125.28</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>43.52</v>
+        <v>143.96</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>43.52</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.09</v>
+        <v>806.4400000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.09</v>
+        <v>764.24</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.17</v>
+        <v>822.55</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.17</v>
+        <v>825.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1517.5</v>
+        <v>1771.18</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1429.82</v>
+        <v>1683.12</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1607.2</v>
+        <v>1838.8</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1595</v>
+        <v>1840.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SAPPL</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>309.58</v>
+        <v>78.17</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>286.84</v>
+        <v>78.17</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>327.1</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>320.1</v>
+        <v>81.29000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>OMFREIGHT</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1058.21</v>
+        <v>99.55</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1058.19</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1058.76</v>
+        <v>105</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1058.77</v>
+        <v>105.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1252.68</v>
+        <v>616.51</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1201.96</v>
+        <v>576.23</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1268.1</v>
+        <v>656.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1281.7</v>
+        <v>655.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>65.12</v>
+        <v>42.12</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>59.85</v>
+        <v>40.15</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>71</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>801.35</v>
+        <v>2.13</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>752.84</v>
+        <v>2.13</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>812.9</v>
+        <v>2.21</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>814.3</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>7.44</v>
+        <v>1575.14</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>7.35</v>
+        <v>1478.66</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>8.17</v>
+        <v>1612.1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.17</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,16 +1508,103 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>21.89</v>
+        <v>1058.44</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>21.11</v>
+        <v>1058.42</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>23.98</v>
+        <v>1058.89</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>24</v>
+        <v>1058.89</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>72.87</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TICL</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>VELJAN</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2303.84</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2204.9</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2531.4</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>2531.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15.48</v>
+        <v>16.16</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>15.41</v>
+        <v>16.16</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>16.92</v>
+        <v>17.76</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>16.92</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1295.14</v>
+        <v>1318.7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1256.28</v>
+        <v>1273.7</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1313</v>
+        <v>1341.4</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1313</v>
+        <v>1341.4</v>
       </c>
     </row>
     <row r="4">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>715.76</v>
+        <v>741.16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>681.49</v>
+        <v>701.42</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>753.7</v>
+        <v>798.05</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>762.95</v>
+        <v>796</v>
       </c>
     </row>
     <row r="5">
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1079.42</v>
+        <v>1079.65</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1079.4</v>
+        <v>1079.63</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1079.86</v>
+        <v>1080.02</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1079.85</v>
+        <v>1080.03</v>
       </c>
     </row>
     <row r="6">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>378.92</v>
+        <v>386.46</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>378.71</v>
+        <v>386.25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>394</v>
+        <v>401.85</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>394</v>
+        <v>401.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6.9</v>
+        <v>20.13</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.9</v>
+        <v>18.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7.17</v>
+        <v>22.02</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7.17</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>26.08</v>
+        <v>4899.06</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>26.08</v>
+        <v>4789.64</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>27.12</v>
+        <v>4872.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>27.12</v>
+        <v>4872.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13915.8</v>
+        <v>7.04</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>13398.4</v>
+        <v>7.04</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>14279</v>
+        <v>7.31</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14318</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1050.24</v>
+        <v>26.6</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1050.22</v>
+        <v>26.6</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1050.67</v>
+        <v>27.66</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1050.68</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>477.72</v>
+        <v>1050.46</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>439.31</v>
+        <v>1050.44</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>515.95</v>
+        <v>1050.83</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>513</v>
+        <v>1050.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3.02</v>
+        <v>495.47</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3.01</v>
+        <v>456.41</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3.13</v>
+        <v>499.35</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3.13</v>
+        <v>497.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>684.45</v>
+        <v>3.08</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>670.67</v>
+        <v>3.07</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>693.05</v>
+        <v>3.19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>692</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>304.87</v>
+        <v>690.5</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>291.48</v>
+        <v>676.39</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>315.3</v>
+        <v>689.7</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>312.5</v>
+        <v>697</v>
       </c>
     </row>
     <row r="15">
@@ -899,16 +899,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>238.93</v>
+        <v>250.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>228.62</v>
+        <v>241.62</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>262.78</v>
+        <v>271.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>262.78</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16">
@@ -928,16 +928,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>35.27</v>
+        <v>37.03</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>33.58</v>
+        <v>35.84</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>38.78</v>
+        <v>40.71</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>38.78</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="17">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>211.8</v>
+        <v>216.05</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>202.08</v>
+        <v>206.09</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>214.9</v>
+        <v>220.22</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>216.3</v>
+        <v>219.35</v>
       </c>
     </row>
     <row r="18">
@@ -1001,7 +1001,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1057.89</v>
+        <v>1147.65</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1057.84</v>
+        <v>1147.62</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1058.31</v>
+        <v>1148.02</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1058.3</v>
+        <v>1148.02</v>
       </c>
     </row>
     <row r="20">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>116.2</v>
+        <v>116.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>116.18</v>
+        <v>116.21</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>116.23</v>
+        <v>116.25</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>116.25</v>
+        <v>116.26</v>
       </c>
     </row>
     <row r="22">
@@ -1102,16 +1102,16 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1123.96</v>
+        <v>1124.19</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1123.94</v>
+        <v>1124.17</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1124.42</v>
+        <v>1124.55</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1124.42</v>
+        <v>1124.54</v>
       </c>
     </row>
     <row r="23">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>410.16</v>
+        <v>435.63</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>369.15</v>
+        <v>394.35</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>455.7</v>
+        <v>465.45</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>451.5</v>
+        <v>465.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MASPTOP50</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>106.55</v>
+        <v>266.45</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>100.29</v>
+        <v>251.43</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>111.05</v>
+        <v>295.01</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>111.72</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>MASPTOP50</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23.59</v>
+        <v>109.95</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>22.11</v>
+        <v>103.29</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>25.05</v>
+        <v>116.81</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>25.09</v>
+        <v>117.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>212.22</v>
+        <v>24.41</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>204.56</v>
+        <v>22.91</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>216.72</v>
+        <v>25.06</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>218</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>MMWL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>133.79</v>
+        <v>16.37</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>125.28</v>
+        <v>16.14</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>143.96</v>
+        <v>17.99</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>144.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>806.4400000000001</v>
+        <v>139.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>764.24</v>
+        <v>130.83</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>822.55</v>
+        <v>146.97</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>825.95</v>
+        <v>147.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1771.18</v>
+        <v>79.73</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1683.12</v>
+        <v>79.73</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1838.8</v>
+        <v>82.91</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1840.5</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>78.17</v>
+        <v>641.11</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>78.17</v>
+        <v>602.01</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>81.29000000000001</v>
+        <v>657.55</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>81.29000000000001</v>
+        <v>657.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>OMFREIGHT</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>99.55</v>
+        <v>43.73</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>91.98999999999999</v>
+        <v>41.67</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>105</v>
+        <v>47.16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>105.05</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>616.51</v>
+        <v>82.06</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>576.23</v>
+        <v>79.17</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>656.95</v>
+        <v>84.23</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>655.9</v>
+        <v>83.51000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>42.12</v>
+        <v>2.17</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>40.15</v>
+        <v>2.17</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45</v>
+        <v>2.25</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>RELINFRA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>2.13</v>
+        <v>48.92</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2.13</v>
+        <v>48.58</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2.21</v>
+        <v>53.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2.21</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1575.14</v>
+        <v>1058.67</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1478.66</v>
+        <v>1058.65</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1612.1</v>
+        <v>1059.04</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1615</v>
+        <v>1059.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1058.44</v>
+        <v>8.19</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1058.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1058.89</v>
+        <v>8.99</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1058.89</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>VELJAN</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>68.11</v>
+        <v>2416.62</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>62.76</v>
+        <v>2332.5</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>72.58</v>
+        <v>2657.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>72.87</v>
+        <v>2657.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,45 +1566,16 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>7.8</v>
+        <v>6.04</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7.72</v>
+        <v>6</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>8.57</v>
+        <v>6.59</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8.57</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>VELJAN</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>2303.84</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>2204.9</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2531.4</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>2531.4</v>
+        <v>6.59</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>AARVI</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.16</v>
+        <v>140.03</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16.16</v>
+        <v>134.39</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>17.76</v>
+        <v>138.26</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>17.76</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1318.7</v>
+        <v>16.96</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1273.7</v>
+        <v>16.83</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1341.4</v>
+        <v>18.64</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1341.4</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>741.16</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>701.42</v>
+        <v>7.45</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>798.05</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>796</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="5">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1079.65</v>
+        <v>1079.88</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1079.63</v>
+        <v>1079.86</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1080.02</v>
+        <v>1080.17</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1080.03</v>
+        <v>1080.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>386.46</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>386.25</v>
+        <v>91.37</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>401.85</v>
+        <v>95.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>401.85</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>AVADHSUGAR</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>20.13</v>
+        <v>894.89</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18.9</v>
+        <v>834.47</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22.02</v>
+        <v>939.55</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>22.02</v>
+        <v>943.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4899.06</v>
+        <v>394.15</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>4789.64</v>
+        <v>393.94</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4872.2</v>
+        <v>409.85</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4872.2</v>
+        <v>409.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7.04</v>
+        <v>3277.32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7.04</v>
+        <v>3160</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7.31</v>
+        <v>3334.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.31</v>
+        <v>3334.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26.6</v>
+        <v>21.07</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>26.6</v>
+        <v>19.92</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>27.66</v>
+        <v>23.08</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>27.66</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1050.46</v>
+        <v>7.17</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1050.44</v>
+        <v>7.17</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1050.83</v>
+        <v>7.45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1050.84</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>495.47</v>
+        <v>27.13</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>456.41</v>
+        <v>27.13</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>499.35</v>
+        <v>28.21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>497.45</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3.08</v>
+        <v>699.11</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3.07</v>
+        <v>661.77</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3.19</v>
+        <v>714.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3.19</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>690.5</v>
+        <v>1050.69</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>676.39</v>
+        <v>1050.65</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>689.7</v>
+        <v>1050.97</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>697</v>
+        <v>1050.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>250.87</v>
+        <v>3.13</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>241.62</v>
+        <v>3.11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>271.9</v>
+        <v>3.25</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>269</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>37.03</v>
+        <v>265.01</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>35.84</v>
+        <v>254.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>40.71</v>
+        <v>266.35</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>40.71</v>
+        <v>263.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>GILLETTE</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>216.05</v>
+        <v>7144</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>206.09</v>
+        <v>6949</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>220.22</v>
+        <v>7263.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>219.35</v>
+        <v>7290</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.06</v>
+        <v>192.92</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.06</v>
+        <v>184.99</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.08</v>
+        <v>192.6</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.08</v>
+        <v>193.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1147.65</v>
+        <v>111.05</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1147.62</v>
+        <v>110.94</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1148.02</v>
+        <v>111.07</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1148.02</v>
+        <v>111.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1010.06</v>
+        <v>482.46</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1010.06</v>
+        <v>461.61</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1010.85</v>
+        <v>492.1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1010.85</v>
+        <v>490.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>116.23</v>
+        <v>32.65</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>116.21</v>
+        <v>30.29</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>116.25</v>
+        <v>34.88</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>116.26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>ICEMAKE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1124.19</v>
+        <v>654.96</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1124.17</v>
+        <v>622.27</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1124.55</v>
+        <v>660.25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1124.54</v>
+        <v>653.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>435.63</v>
+        <v>344.21</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>394.35</v>
+        <v>312.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>465.45</v>
+        <v>356.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>465.95</v>
+        <v>353.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>KAVDEFENCE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>266.45</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>251.43</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>295.01</v>
+        <v>93.66</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>296</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MASPTOP50</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>109.95</v>
+        <v>0.06</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>103.29</v>
+        <v>0.06</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>116.81</v>
+        <v>0.08</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>117.88</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>24.41</v>
+        <v>1147.89</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>22.91</v>
+        <v>1147.86</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>25.06</v>
+        <v>1148.18</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>25</v>
+        <v>1148.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.37</v>
+        <v>1010.44</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>16.14</v>
+        <v>1010.43</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>17.99</v>
+        <v>1011.11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17.99</v>
+        <v>1011.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>139.4</v>
+        <v>116.25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>130.83</v>
+        <v>116.23</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>146.97</v>
+        <v>116.27</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>147.51</v>
+        <v>116.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>79.73</v>
+        <v>1124.42</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>79.73</v>
+        <v>1124.4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>82.91</v>
+        <v>1124.71</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>82.91</v>
+        <v>1124.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>641.11</v>
+        <v>294.76</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>602.01</v>
+        <v>266.44</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>657.55</v>
+        <v>292.31</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>657.55</v>
+        <v>290.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>MMWL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>43.73</v>
+        <v>17.36</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>41.67</v>
+        <v>17.14</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>47.16</v>
+        <v>19.77</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>46.9</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>MONQ50</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>82.06</v>
+        <v>236.39</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>79.17</v>
+        <v>204.26</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>84.23</v>
+        <v>243.73</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>83.51000000000001</v>
+        <v>241.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.17</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2.17</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2.25</v>
+        <v>84.56</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2.25</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RELINFRA</t>
+          <t>ONEGLOBAL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>48.92</v>
+        <v>571.38</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>48.58</v>
+        <v>536.87</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>53.8</v>
+        <v>561.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>53.8</v>
+        <v>556.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1058.67</v>
+        <v>45.53</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1058.65</v>
+        <v>43.39</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1059.04</v>
+        <v>49.51</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1059.04</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>8.19</v>
+        <v>299.51</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>281.49</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>8.99</v>
+        <v>303.25</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.99</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>VELJAN</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,45 +1537,364 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2416.62</v>
+        <v>2.21</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2332.5</v>
+        <v>2.21</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2657.9</v>
+        <v>2.29</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2657.9</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>PNGSREVA</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>603.65</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>541.8200000000001</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>701.95</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>676.95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>134.85</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>126.41</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>140.48</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RAJOOENG</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RAMBHAJO</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>311.28</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>356.55</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>354.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RELINFRA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>56.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1058.91</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1058.89</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1059.18</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1059.18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SILINV</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>458.82</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>438.96</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>462.1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>STUDDS</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>417.08</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>398.83</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>416</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>418.95</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>VELJAN</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2537.4</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2468.5</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2762.9</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>2790.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>VIDYAWIRES</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>VIVIMEDLAB</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>6.59</v>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>VMART</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>794.92</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>760.25</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>811.15</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>822.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AARVI</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>140.03</v>
+        <v>1081.08</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>134.39</v>
+        <v>1080.06</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>138.26</v>
+        <v>1080.61</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>138.02</v>
+        <v>1080.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.96</v>
+        <v>402</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>16.83</v>
+        <v>401.79</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18.64</v>
+        <v>418</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18.64</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.039999999999999</v>
+        <v>881.98</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.45</v>
+        <v>824.98</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9</v>
+        <v>892.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.08</v>
+        <v>887.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1079.88</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1079.86</v>
+        <v>58.95</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1080.17</v>
+        <v>70.13</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1080.18</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>95.81999999999999</v>
+        <v>21.94</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>91.37</v>
+        <v>20.84</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>95.62</v>
+        <v>23.54</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>95.15000000000001</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AVADHSUGAR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>894.89</v>
+        <v>27.67</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>834.47</v>
+        <v>27.67</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>939.55</v>
+        <v>28.77</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>943.75</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>394.15</v>
+        <v>1050.9</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>393.94</v>
+        <v>1050.85</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>409.85</v>
+        <v>1051.42</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>409.85</v>
+        <v>1051.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3277.32</v>
+        <v>1.76</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3160</v>
+        <v>1.7</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3334.8</v>
+        <v>1.91</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3334.8</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>21.07</v>
+        <v>3.19</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.92</v>
+        <v>3.16</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>23.08</v>
+        <v>3.25</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>23.12</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.17</v>
+        <v>111.07</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7.17</v>
+        <v>111.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.45</v>
+        <v>111.11</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7.45</v>
+        <v>111.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>KAVDEFENCE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>27.13</v>
+        <v>89.81</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>27.13</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>28.21</v>
+        <v>92.19</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.21</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>699.11</v>
+        <v>0.06</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>661.77</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>714.15</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>725</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1050.69</v>
+        <v>1148.1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1050.65</v>
+        <v>1148.08</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1050.97</v>
+        <v>1148.65</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1050.97</v>
+        <v>1148.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.13</v>
+        <v>1010.82</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3.11</v>
+        <v>1010.82</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3.25</v>
+        <v>1011.55</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3.25</v>
+        <v>1011.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>265.01</v>
+        <v>116.27</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>254.67</v>
+        <v>116.25</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>266.35</v>
+        <v>116.32</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>263.4</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GILLETTE</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7144</v>
+        <v>1124.63</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6949</v>
+        <v>1124.61</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7263.5</v>
+        <v>1125.13</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>7290</v>
+        <v>1125.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>192.92</v>
+        <v>82.94</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>184.99</v>
+        <v>82.94</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>192.6</v>
+        <v>86.25</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>193.2</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>111.05</v>
+        <v>47.53</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>110.94</v>
+        <v>45.29</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>111.07</v>
+        <v>50.06</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>111.08</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>482.46</v>
+        <v>301.05</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>461.61</v>
+        <v>290.23</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>492.1</v>
+        <v>307</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>490.2</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.65</v>
+        <v>2.25</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>30.29</v>
+        <v>2.25</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>34.88</v>
+        <v>2.33</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ICEMAKE</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>654.96</v>
+        <v>349.51</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>622.27</v>
+        <v>324.68</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>660.25</v>
+        <v>357.45</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>653.95</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>RELINFRA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>344.21</v>
+        <v>53.92</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>312.4</v>
+        <v>52.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>356.9</v>
+        <v>59.29</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>353.8</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>1059.12</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>82.54000000000001</v>
+        <v>1059.1</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>93.66</v>
+        <v>1059.62</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>92.2</v>
+        <v>1059.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>TECHNVISN</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.06</v>
+        <v>4225.22</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.06</v>
+        <v>4009.3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.08</v>
+        <v>4487.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.08</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1147.89</v>
+        <v>174.25</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1147.86</v>
+        <v>160.83</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1148.18</v>
+        <v>181.76</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1148.2</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,654 +1247,16 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1010.44</v>
+        <v>812.23</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1010.43</v>
+        <v>773.13</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1011.11</v>
+        <v>821.95</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1011.11</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDCASE</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>116.25</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>116.23</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>116.27</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>116.28</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>LIQUIDSHRI</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>1124.42</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>1124.4</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1124.71</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>1124.72</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>MEGASTAR</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>294.76</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>266.44</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>292.31</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>290.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>MMWL</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>17.36</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>19.77</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>19.78</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>MONQ50</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>236.39</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>204.26</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>243.73</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>241.99</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>OILCOUNTUB</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>81.31999999999999</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>81.31999999999999</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>84.56</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>84.56</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ONEGLOBAL</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>571.38</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>536.87</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>561.3</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>556.05</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ONELIFECAP</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>43.39</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>49.51</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>PARAGMILK</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>299.51</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>281.49</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>303.25</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>PARSVNATH</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>PNGSREVA</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>603.65</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>541.8200000000001</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>701.95</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>676.95</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>PWL</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>134.85</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>126.41</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>140.48</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RAJOOENG</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>59.53</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>59.92</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>RAMBHAJO</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>335.22</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>311.28</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>356.55</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>354.8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RELINFRA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>56.49</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1058.91</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1058.89</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1059.18</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1059.18</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SILINV</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>458.82</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>438.96</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>462.1</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>STUDDS</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>417.08</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>398.83</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>416</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>418.95</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>VELJAN</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>2537.4</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2468.5</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2762.9</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2790.7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>VIDYAWIRES</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>93.15000000000001</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>98.03</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>VIVIMEDLAB</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>6.91</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>VMART</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>794.92</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>760.25</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>811.15</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>822.85</v>
+        <v>817.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ANNU</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1081.08</v>
+        <v>47.13</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1080.06</v>
+        <v>44.69</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1080.61</v>
+        <v>46.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1080.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>402</v>
+        <v>410.01</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>401.79</v>
+        <v>409.8</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>418</v>
+        <v>426.35</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>418</v>
+        <v>426.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>881.98</v>
+        <v>265.68</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>824.98</v>
+        <v>256.85</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>892.1</v>
+        <v>286.05</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>887.8</v>
+        <v>286.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>22.73</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>58.95</v>
+        <v>21.76</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70.13</v>
+        <v>23.07</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>69.8</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.94</v>
+        <v>28.22</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20.84</v>
+        <v>28.22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>23.54</v>
+        <v>29.34</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>23.54</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>27.67</v>
+        <v>1051.11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>27.67</v>
+        <v>1051.07</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>28.77</v>
+        <v>1051.62</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>28.77</v>
+        <v>1051.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1050.9</v>
+        <v>111.09</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1050.85</v>
+        <v>111.08</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1051.42</v>
+        <v>111.13</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1051.41</v>
+        <v>111.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.76</v>
+        <v>49.67</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.7</v>
+        <v>46.51</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.91</v>
+        <v>51.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1.92</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.19</v>
+        <v>426.46</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.16</v>
+        <v>409.24</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3.25</v>
+        <v>435.85</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3.25</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>111.07</v>
+        <v>0.06</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>111.06</v>
+        <v>0.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>111.11</v>
+        <v>0.08</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>111.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>89.81</v>
+        <v>1148.36</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>85.43000000000001</v>
+        <v>1148.3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>92.19</v>
+        <v>1148.82</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>1148.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.06</v>
+        <v>1010.82</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.06</v>
+        <v>1010.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.08</v>
+        <v>1011.55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.08</v>
+        <v>1011.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1148.1</v>
+        <v>116.3</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1148.08</v>
+        <v>116.28</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1148.65</v>
+        <v>116.34</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1148.64</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1010.82</v>
+        <v>1124.83</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1010.82</v>
+        <v>1124.81</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1011.55</v>
+        <v>1125.29</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1011.55</v>
+        <v>1125.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MLKFOOD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>116.27</v>
+        <v>86.98</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>116.25</v>
+        <v>83.97</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>116.32</v>
+        <v>86.13</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>116.33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1124.63</v>
+        <v>309.45</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1124.61</v>
+        <v>294.74</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1125.13</v>
+        <v>332.45</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1125.13</v>
+        <v>331.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>82.94</v>
+        <v>2.29</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>82.94</v>
+        <v>2.29</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>86.25</v>
+        <v>2.37</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>86.25</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>47.53</v>
+        <v>14.27</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>45.29</v>
+        <v>13.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>50.06</v>
+        <v>15</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>50.25</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>301.05</v>
+        <v>1159.86</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>290.23</v>
+        <v>1127.72</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>307</v>
+        <v>1200</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>307</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2.25</v>
+        <v>20.82</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2.25</v>
+        <v>20.76</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.33</v>
+        <v>21.64</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2.33</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="22">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>349.51</v>
+        <v>361.07</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>324.68</v>
+        <v>339.09</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>357.45</v>
+        <v>375.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>357</v>
+        <v>375.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RELINFRA</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>53.92</v>
+        <v>1059.32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>52.8</v>
+        <v>1059.3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>59.29</v>
+        <v>1059.77</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.29</v>
+        <v>1059.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>TOYAMSL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1059.12</v>
+        <v>0.74</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1059.1</v>
+        <v>0.71</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1059.62</v>
+        <v>0.79</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1059.62</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TECHNVISN</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4225.22</v>
+        <v>184.68</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4009.3</v>
+        <v>166.65</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4487.7</v>
+        <v>218.11</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>4451</v>
+        <v>218.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW</t>
+          <t>VERANDA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>174.25</v>
+        <v>32.83</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>160.83</v>
+        <v>31.86</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>181.76</v>
+        <v>36.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>184.5</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,16 +1247,45 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>812.23</v>
+        <v>138.32</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>773.13</v>
+        <v>133.92</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>821.95</v>
+        <v>150.04</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>817.5</v>
+        <v>150.04</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>97.98</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANNU</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>47.13</v>
+        <v>151.22</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>44.69</v>
+        <v>140.07</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46.6</v>
+        <v>153.98</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.5</v>
+        <v>155.88</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>410.01</v>
+        <v>418.18</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>409.8</v>
+        <v>418.17</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>426.35</v>
+        <v>434.85</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>426.35</v>
+        <v>434.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>265.68</v>
+        <v>28.78</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>256.85</v>
+        <v>28.78</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>286.05</v>
+        <v>29.92</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>286.05</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>22.73</v>
+        <v>1051.93</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>21.76</v>
+        <v>1051.28</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23.07</v>
+        <v>1051.77</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23.07</v>
+        <v>1051.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>28.22</v>
+        <v>111.11</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28.22</v>
+        <v>111.1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>29.34</v>
+        <v>111.14</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>29.34</v>
+        <v>111.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1051.11</v>
+        <v>1030.27</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1051.07</v>
+        <v>1005.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1051.62</v>
+        <v>1062.1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1051.62</v>
+        <v>1062.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>ITADD</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>111.09</v>
+        <v>30.62</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>111.08</v>
+        <v>29.77</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>111.13</v>
+        <v>31.54</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>111.14</v>
+        <v>31.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>49.67</v>
+        <v>0.06</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46.51</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>51.8</v>
+        <v>0.08</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>52</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>426.46</v>
+        <v>1148.58</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>409.24</v>
+        <v>1148.52</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>435.85</v>
+        <v>1148.97</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>441</v>
+        <v>1148.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.06</v>
+        <v>116.32</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.06</v>
+        <v>116.3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.08</v>
+        <v>116.34</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.08</v>
+        <v>116.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1148.36</v>
+        <v>1125.04</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1148.3</v>
+        <v>1125.02</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1148.82</v>
+        <v>1125.44</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1148.83</v>
+        <v>1125.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>METROBRAND</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1010.82</v>
+        <v>880.38</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1010.82</v>
+        <v>827.5599999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1011.55</v>
+        <v>887.35</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1011.55</v>
+        <v>960</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>116.3</v>
+        <v>318.01</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>116.28</v>
+        <v>301.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>116.34</v>
+        <v>326.95</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>116.35</v>
+        <v>325.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1124.83</v>
+        <v>2.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1124.81</v>
+        <v>2.33</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1125.29</v>
+        <v>2.41</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1125.29</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MLKFOOD</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>86.98</v>
+        <v>1182.38</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>83.97</v>
+        <v>1148.48</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>86.13</v>
+        <v>1224.8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>86</v>
+        <v>1224.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>309.45</v>
+        <v>21.23</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>294.74</v>
+        <v>21.23</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>332.45</v>
+        <v>22.07</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>331.1</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.29</v>
+        <v>1059.52</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.29</v>
+        <v>1059.5</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2.37</v>
+        <v>1059.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2.37</v>
+        <v>1059.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>SIMPLXREA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14.27</v>
+        <v>131.92</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13.6</v>
+        <v>129.3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>15</v>
+        <v>144.8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.93</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1159.86</v>
+        <v>2881.96</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1127.72</v>
+        <v>2729.22</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1200</v>
+        <v>2968.2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1200</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.82</v>
+        <v>201.65</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20.76</v>
+        <v>178.6</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>21.64</v>
+        <v>229.79</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>21.64</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>361.07</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>339.09</v>
+        <v>23.5</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>375.3</v>
+        <v>25.82</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>375.3</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>VERANDA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,161 +1131,16 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1059.32</v>
+        <v>34.47</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1059.3</v>
+        <v>34.06</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1059.77</v>
+        <v>37.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1059.77</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TOYAMSL</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>UDAYJEW</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>184.68</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>166.65</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>218.11</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>218.11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>VERANDA</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>32.83</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>36.1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>138.32</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>133.92</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>150.04</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>150.04</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>94.84999999999999</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>91.16</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>98.23</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>97.98</v>
+        <v>37.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,30 +508,639 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>50.87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2157.96</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2121.76</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BHAGYANGR</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>60.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DSKULKARNI</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>33.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1382.08</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1332.82</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1424.2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1424.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HDFCNIFIT</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ICDSLTD</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>49.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ITBEES</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>35.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1225.44</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1191.08</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1222.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>KSHITIJ-RE</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>0.08</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDADD</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1149.77</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1149.7</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1150.32</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1150.31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDCASE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>116.42</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>116.49</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>116.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1126.16</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1126.14</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1126.7</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1126.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MAHASTEEL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1234.42</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1355.2</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1357.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MASTEK</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1814.82</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1748.82</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1847.2</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>NINSYS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>865.13</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>816.22</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>870.85</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>874.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PARACABLES</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>62.77</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PRISMX</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3748.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>3624.2</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>3848.6</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>3848.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2434.2</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2354.86</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2529</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>35.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABMINTLLTD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46.88</v>
+        <v>43.4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>45.06</v>
+        <v>43.39</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>50.87</v>
+        <v>46.85</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>50.87</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2157.96</v>
+        <v>2184.2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2121.76</v>
+        <v>2143.34</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2200</v>
+        <v>2223</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2200</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="4">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>54.97</v>
+        <v>58.19</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>54.97</v>
+        <v>58.19</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>60.95</v>
+        <v>63.95</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>60.95</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="5">
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>31.63</v>
+        <v>32.38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>31.63</v>
+        <v>32.38</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>33.01</v>
+        <v>33.67</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33.01</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="6">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1382.08</v>
+        <v>1402.46</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1332.82</v>
+        <v>1364.24</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1424.2</v>
+        <v>1421.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1424.2</v>
+        <v>1421.7</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>33.63</v>
+        <v>34.24</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>32.36</v>
+        <v>33.22</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>34.4</v>
+        <v>34.17</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>47.16</v>
+        <v>35.72</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>45.32</v>
+        <v>34.49</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>50.74</v>
+        <v>35.56</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>49.75</v>
+        <v>35.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>34.98</v>
+        <v>0.06</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>33.75</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>35.95</v>
+        <v>0.08</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35.97</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1225.44</v>
+        <v>1150.1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1191.08</v>
+        <v>1150</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1222.9</v>
+        <v>1150.48</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1222.9</v>
+        <v>1150.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.06</v>
+        <v>1012.7</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.06</v>
+        <v>1012.64</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.08</v>
+        <v>1013.17</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.08</v>
+        <v>1013.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1149.77</v>
+        <v>116.47</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1149.7</v>
+        <v>116.45</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1150.32</v>
+        <v>116.51</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1150.31</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>116.44</v>
+        <v>1126.44</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>116.42</v>
+        <v>1126.42</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>116.49</v>
+        <v>1126.87</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>116.49</v>
+        <v>1126.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1126.16</v>
+        <v>1295.62</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1126.14</v>
+        <v>1230.6</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1126.7</v>
+        <v>1420.5</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1126.7</v>
+        <v>1422.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1234.42</v>
+        <v>17.95</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1170</v>
+        <v>16.25</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1355.2</v>
+        <v>18.07</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1357.4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>QUINTEGRA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1814.82</v>
+        <v>2.24</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1748.82</v>
+        <v>2.24</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1847.2</v>
+        <v>2.45</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1854</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>865.13</v>
+        <v>3842.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>816.22</v>
+        <v>3737.94</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>870.85</v>
+        <v>3846.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>874.95</v>
+        <v>3846.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,161 +986,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>62.77</v>
+        <v>35.07</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>58.03</v>
+        <v>34.04</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>35.04</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>PASHUPATI</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>85.04000000000001</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>81.42</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>94.17</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>PRISMX</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>3748.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>3624.2</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>3848.6</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>3848.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>2434.2</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>2354.86</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>2529</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>34.53</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>33.36</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>35.06</v>
+        <v>34.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>43.4</v>
+        <v>44.94</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>43.39</v>
+        <v>44.93</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46.85</v>
+        <v>49.19</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.85</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2184.2</v>
+        <v>2203.6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2143.34</v>
+        <v>2165.7</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2223</v>
+        <v>2235</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2223</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="4">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>58.19</v>
+        <v>61.07</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>58.19</v>
+        <v>61.07</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>63.95</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>63.95</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32.38</v>
+        <v>33.03</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>32.38</v>
+        <v>33.03</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>33.67</v>
+        <v>34.34</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33.67</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="6">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1402.46</v>
+        <v>1420.78</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1364.24</v>
+        <v>1381.58</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1421.7</v>
+        <v>1422.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1421.7</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HDFCNIFIT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>34.24</v>
+        <v>36.09</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>33.22</v>
+        <v>34.76</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>34.17</v>
+        <v>35.56</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>34.1</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="8">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>35.72</v>
+        <v>36.2</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>34.49</v>
+        <v>34.88</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>35.56</v>
+        <v>35.62</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>35.55</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="9">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1150.1</v>
+        <v>1150.43</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1150</v>
+        <v>1150.33</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1150.48</v>
+        <v>1150.98</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1150.49</v>
+        <v>1150.99</v>
       </c>
     </row>
     <row r="11">
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1012.7</v>
+        <v>1013.07</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1012.64</v>
+        <v>1013.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1013.17</v>
+        <v>1013.65</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1013.17</v>
+        <v>1013.65</v>
       </c>
     </row>
     <row r="12">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>116.47</v>
+        <v>116.5</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>116.45</v>
+        <v>116.48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>116.51</v>
+        <v>116.55</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>116.51</v>
+        <v>116.57</v>
       </c>
     </row>
     <row r="13">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1126.44</v>
+        <v>1126.76</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1126.42</v>
+        <v>1126.74</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1126.87</v>
+        <v>1127.35</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1126.88</v>
+        <v>1127.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>QUINTEGRA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1295.62</v>
+        <v>2.34</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1230.6</v>
+        <v>2.34</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1420.5</v>
+        <v>2.57</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1422.9</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,103 +899,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>17.95</v>
+        <v>1061.23</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>16.25</v>
+        <v>1061.19</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>18.07</v>
+        <v>1061.78</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUINTEGRA</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>3842.2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>3737.94</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>3846.8</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>3846.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>34.04</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>34.9</v>
+        <v>1061.78</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>44.94</v>
+        <v>46.96</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>44.93</v>
+        <v>46.95</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>49.19</v>
+        <v>51.64</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>49.19</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2203.6</v>
+        <v>1082.41</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2165.7</v>
+        <v>1082.38</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2235</v>
+        <v>1082.9</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2235</v>
+        <v>1082.9</v>
       </c>
     </row>
     <row r="4">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>61.07</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61.07</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>70.45</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>33.03</v>
+        <v>2053.3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>33.03</v>
+        <v>2004.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>34.34</v>
+        <v>2041.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>34.34</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1420.78</v>
+        <v>33.03</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1381.58</v>
+        <v>33.03</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1422.2</v>
+        <v>34.34</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1422.2</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36.09</v>
+        <v>1053.4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>34.76</v>
+        <v>1052.31</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>35.56</v>
+        <v>1054.4</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>35.47</v>
+        <v>1054.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>36.2</v>
+        <v>0.06</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>34.88</v>
+        <v>0.06</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>35.62</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>35.7</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.06</v>
+        <v>1013.07</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.06</v>
+        <v>1013.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.08</v>
+        <v>1013.65</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.08</v>
+        <v>1013.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1150.43</v>
+        <v>116.53</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1150.33</v>
+        <v>116.51</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1150.98</v>
+        <v>116.58</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1150.99</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1013.07</v>
+        <v>1127.01</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1013.06</v>
+        <v>1126.99</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1013.65</v>
+        <v>1127.51</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1013.65</v>
+        <v>1127.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>QUINTEGRA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>116.5</v>
+        <v>2.46</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>116.48</v>
+        <v>2.46</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>116.55</v>
+        <v>2.69</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>116.57</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,74 +841,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1126.76</v>
+        <v>1061.48</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1126.74</v>
+        <v>1061.44</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1127.35</v>
+        <v>1061.95</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1127.34</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>QUINTEGRA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>1061.23</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>1061.19</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1061.78</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>1061.78</v>
+        <v>1061.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABMINTLLTD</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46.96</v>
+        <v>1082.63</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46.95</v>
+        <v>1082.61</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>51.64</v>
+        <v>1083.07</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>51.64</v>
+        <v>1083.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1082.41</v>
+        <v>2082.72</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1082.38</v>
+        <v>2015.24</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1082.9</v>
+        <v>2152</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1082.9</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>33.68</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>33.68</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>70.45</v>
+        <v>35.02</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>70.45</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2053.3</v>
+        <v>1053.75</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2004.22</v>
+        <v>1053.67</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2041.4</v>
+        <v>1054.56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2050</v>
+        <v>1054.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>33.03</v>
+        <v>376.63</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>33.03</v>
+        <v>348.31</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>34.34</v>
+        <v>392.55</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>34.34</v>
+        <v>390.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>JINDALPHOT</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1053.4</v>
+        <v>1084.54</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1052.31</v>
+        <v>1038.46</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1054.4</v>
+        <v>1114.4</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1054.39</v>
+        <v>1112.9</v>
       </c>
     </row>
     <row r="8">
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1013.07</v>
+        <v>1013.34</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1013.06</v>
+        <v>1013.33</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1013.65</v>
+        <v>1013.95</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1013.65</v>
+        <v>1013.95</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>116.53</v>
+        <v>116.56</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>116.51</v>
+        <v>116.54</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>116.58</v>
+        <v>116.59</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>116.59</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="11">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1127.01</v>
+        <v>1127.23</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1126.99</v>
+        <v>1127.22</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1127.51</v>
+        <v>1127.68</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1127.51</v>
+        <v>1127.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>QUINTEGRA</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,45 +812,103 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2.46</v>
+        <v>2.73</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>QUINTEGRA</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SASKEN</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1831.42</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1691.94</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1904.4</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>SBILIQETF</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1061.48</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>1061.44</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>1061.95</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1061.94</v>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1061.7</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1061.66</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1062.12</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1062.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1082.63</v>
+        <v>1082.86</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1082.61</v>
+        <v>1082.83</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1083.07</v>
+        <v>1083.22</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1083.06</v>
+        <v>1083.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2082.72</v>
+        <v>2317.3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2015.24</v>
+        <v>2237.14</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2152</v>
+        <v>2362.8</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2155</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.68</v>
+        <v>2117.4</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.68</v>
+        <v>2047.28</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>35.02</v>
+        <v>2200.6</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>35.02</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1053.75</v>
+        <v>34.35</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1053.67</v>
+        <v>34.35</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1054.56</v>
+        <v>35.72</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1054.55</v>
+        <v>35.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>376.63</v>
+        <v>5.72</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>348.31</v>
+        <v>5.42</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>392.55</v>
+        <v>5.81</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>390.5</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>JINDALPHOT</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1084.54</v>
+        <v>1054.09</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1038.46</v>
+        <v>1053.99</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1114.4</v>
+        <v>1054.72</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1112.9</v>
+        <v>1054.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.06</v>
+        <v>741.34</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.06</v>
+        <v>723.8200000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.08</v>
+        <v>751.35</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.08</v>
+        <v>751.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1013.34</v>
+        <v>28.36</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1013.33</v>
+        <v>26.3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1013.95</v>
+        <v>29.63</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1013.95</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>116.56</v>
+        <v>65.48</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>116.54</v>
+        <v>58.67</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>116.59</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>116.6</v>
+        <v>75.29000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>JINDALPHOT</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1127.23</v>
+        <v>1101.04</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1127.22</v>
+        <v>1057.16</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1127.68</v>
+        <v>1123.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1127.69</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2.73</v>
+        <v>0.06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.68</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2.83</v>
+        <v>0.08</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2.83</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QUINTEGRA</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.57</v>
+        <v>1061.23</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.57</v>
+        <v>1061.12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.82</v>
+        <v>1061.6</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2.82</v>
+        <v>1061.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1831.42</v>
+        <v>1013.58</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1691.94</v>
+        <v>1013.57</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1904.4</v>
+        <v>1014.09</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1908</v>
+        <v>1014.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,16 +899,335 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1061.7</v>
+        <v>116.58</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1061.66</v>
+        <v>116.56</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1062.12</v>
+        <v>116.61</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1062.12</v>
+        <v>116.62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1127.46</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1127.44</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1127.83</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1127.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>11368.2</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>11105.4</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>11579</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>11579</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>114.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>104.14</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>121.58</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>121.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>QUINTEGRA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>342.98</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>386.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>154.87</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>147.82</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>156.94</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>157.51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>11120.6</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>10885</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>11104</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11104</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>UYFINCORP</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>27.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1424.02</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1376.48</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1442.8</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1442</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1082.86</v>
+        <v>172.71</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1082.83</v>
+        <v>160.47</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1083.22</v>
+        <v>180.38</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1083.21</v>
+        <v>181.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2317.3</v>
+        <v>66.28</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2237.14</v>
+        <v>63.46</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2362.8</v>
+        <v>68.25</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2351</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2117.4</v>
+        <v>1145.34</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2047.28</v>
+        <v>1109.32</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2200.6</v>
+        <v>1182</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>34.35</v>
+        <v>1084.12</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>34.35</v>
+        <v>1083.06</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>35.72</v>
+        <v>1083.38</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35.72</v>
+        <v>1083.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5.72</v>
+        <v>2163.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5.42</v>
+        <v>2086.88</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.81</v>
+        <v>2195</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5.81</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1054.09</v>
+        <v>505.94</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1053.99</v>
+        <v>480.11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1054.72</v>
+        <v>503.55</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1054.72</v>
+        <v>500.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>741.34</v>
+        <v>3436.8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>723.8200000000001</v>
+        <v>3337.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>751.35</v>
+        <v>3502</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>751.8</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28.36</v>
+        <v>2346.68</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>26.3</v>
+        <v>2270.72</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>29.63</v>
+        <v>2376.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>28.68</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>65.48</v>
+        <v>1086.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>58.67</v>
+        <v>1085.84</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>76.34999999999999</v>
+        <v>1086.17</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>75.29000000000001</v>
+        <v>1086.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>JINDALPHOT</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1101.04</v>
+        <v>476.78</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1057.16</v>
+        <v>458.57</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1123.3</v>
+        <v>481.35</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1127</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.06</v>
+        <v>2156.52</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.06</v>
+        <v>2080.02</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.08</v>
+        <v>2217.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.08</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1061.23</v>
+        <v>145.37</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1061.12</v>
+        <v>138.08</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1061.6</v>
+        <v>143.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1061.59</v>
+        <v>144.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1013.58</v>
+        <v>147.24</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1013.57</v>
+        <v>140.15</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1014.09</v>
+        <v>149.42</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1014.08</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>116.58</v>
+        <v>1489.06</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>116.56</v>
+        <v>1413.24</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>116.61</v>
+        <v>1546.6</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>116.62</v>
+        <v>1544.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1127.46</v>
+        <v>5229.4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1127.44</v>
+        <v>5037.6</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1127.83</v>
+        <v>5299.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1127.83</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>11368.2</v>
+        <v>1316.86</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11105.4</v>
+        <v>1275.22</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>11579</v>
+        <v>1345</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>11579</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>108.87</v>
+        <v>35.04</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>103.35</v>
+        <v>35.04</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>114.96</v>
+        <v>36.43</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>114.96</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2.78</v>
+        <v>5.84</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.75</v>
+        <v>5.54</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2.88</v>
+        <v>5.99</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>110.3</v>
+        <v>7195.1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>104.14</v>
+        <v>7048.9</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>121.58</v>
+        <v>7238</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>121.53</v>
+        <v>7238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>QUINTEGRA</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2.7</v>
+        <v>1054.44</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2.7</v>
+        <v>1054.34</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.96</v>
+        <v>1054.87</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2.96</v>
+        <v>1054.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>356.84</v>
+        <v>329.7</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>342.98</v>
+        <v>317.41</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>386.65</v>
+        <v>337.85</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>386.8</v>
+        <v>337.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>154.87</v>
+        <v>748.26</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>147.82</v>
+        <v>733.61</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>156.94</v>
+        <v>761.75</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>157.51</v>
+        <v>762</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>11120.6</v>
+        <v>122.2</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>10885</v>
+        <v>116.32</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>11104</v>
+        <v>124.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11104</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,45 +1189,1814 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>25.59</v>
+        <v>29.05</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>24.63</v>
+        <v>27.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>27.83</v>
+        <v>29.42</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>27.83</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2272.96</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2201.28</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2339</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HDFCMOMENT</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>29.18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HEALTHIETF</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>164.19</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>160.01</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>166.27</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>166.45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HEALTHY</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>HEGAM</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>223.19</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>206.28</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>243.37</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HLEGLAS</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>409.48</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>388.81</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1694.54</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1634.16</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1710.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>INFRABEES</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>907.51</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>887.1900000000001</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>922.08</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>906.05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>INFRAIETF</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>90.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>911.46</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>876.29</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>918.15</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>919.15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>JINDALPHOT</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1118.02</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1071.78</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1130.4</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1130.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>KINGFA</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>6754</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>6528.7</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>6889</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>6885</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>213.27</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>203.48</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>222.63</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>223.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>KSHITIJ-RE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2130.88</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2050.04</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2244</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>672.54</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>645.78</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>681.75</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>LIQGRWBEES</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1061.46</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1061.34</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1061.76</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1061.77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDBETA</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1013.82</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1013.81</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1014.25</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1014.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDCASE</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>116.59</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>116.62</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>116.64</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1127.68</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1127.67</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1127.98</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1127.98</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>LUMAXTECH</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1965.96</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1834.44</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2058.5</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1951.92</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1822</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1949.3</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>304.85</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>292.25</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>315.35</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>167.75</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>174.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MEDANTA</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1261.24</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1210.9</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1299.7</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>MHLXMIRU</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>179.11</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>167.68</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>183.86</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM30</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>28.89</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>NAHARSPING</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>239.67</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>261.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>326.49</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>352.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>111.81</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>106.41</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>116.01</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>110.94</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>127.83</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>127.89</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>PFIZER</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3738.12</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>3646.1</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>3759.8</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>7800.7</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>7547.3</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>7745</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>7745</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>253.7</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>246.35</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>200.57</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>230.78</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>230.05</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PRIMESECU</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>282.78</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>267.68</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>293.25</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>QUINTEGRA</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>RPPL</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SAIPARENT</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>487.53</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>461.01</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>505.7</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>502.25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SBIETFCON</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>112.89</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>111.08</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>114.16</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>114.15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>405.35</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>405.95</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SHALBY</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>114.89</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>121.96</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>920.6</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>884.5599999999999</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>935.6</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>933.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>828.88</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>801.14</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>832.6</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SHREEPUSHK</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>523.48</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>483.32</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>577</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>3841.46</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3641.6</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>4013.7</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>4062.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>STEAMHOUSE</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>142.82</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>133.85</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>146.46</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>147.7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SUDARCOLOR</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>396.71</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>352.13</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1055.98</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>983.84</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1130.1</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TCPLPACK</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>4127.66</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>3904.04</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>4402.4</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>704.49</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>662.66</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>719.45</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>721.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TERASOFT</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>245.94</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>220.41</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>273.83</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>156.47</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>150.73</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>159.66</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>159.98</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2128.36</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2060.8</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2177</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>763.85</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>727.87</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>791.35</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>460.44</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>443.77</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>469.6</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>470.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TTKHLTCARE</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1019.68</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>971.16</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>1049.1</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
           <t>VIJAYA</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>1424.02</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1376.48</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1442.8</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>1442</v>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1438.46</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>1395.58</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1464.2</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>VIYASH</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>208.08</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>224.55</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>224.38</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>WELINV</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1916.06</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>1682.24</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2154.2</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>2164.9</v>
       </c>
     </row>
   </sheetData>
